--- a/results/metrics_modelling4_smote_mean_opt.xlsx
+++ b/results/metrics_modelling4_smote_mean_opt.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH8"/>
+  <dimension ref="A1:DH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,31 +1073,31 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.007159233093261719, 0.006227016448974609, 0.005711078643798828, 0.00559687614440918, 0.0060389041900634766, 0.005403757095336914, 0.005224943161010742</t>
+          <t>0.0067691802978515625, 0.005438089370727539, 0.005393028259277344, 0.005741119384765625, 0.005205869674682617, 0.0058138370513916016, 0.005396842956542969</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.005908829825265067</v>
+        <v>0.005679709570748466</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.005711078643798828</v>
+        <v>0.005438089370727539</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0006024818267958567</v>
+        <v>0.0004860646746321166</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.00837564468383789, 0.009192943572998047, 0.012052059173583984, 0.007241010665893555, 0.008144140243530273, 0.006852149963378906, 0.0074040889739990234</t>
+          <t>0.007107257843017578, 0.0065839290618896484, 0.006695985794067383, 0.006824970245361328, 0.0067403316497802734, 0.006675004959106445, 0.006965160369873047</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0.008466005325317383</v>
+        <v>0.006798948560442243</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.008144140243530273</v>
+        <v>0.006740331649780273</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.001635882941021799</v>
+        <v>0.0001686038391138155</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -1463,31 +1463,31 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.006283998489379883, 0.006273031234741211, 0.011313915252685547, 0.00483393669128418, 0.004912853240966797, 0.004408836364746094, 0.004515171051025391</t>
+          <t>0.007014036178588867, 0.004857778549194336, 0.004539012908935547, 0.005191802978515625, 0.007134914398193359, 0.004791736602783203, 0.005089998245239258</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.006077391760689872</v>
+        <v>0.005517039980207171</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004912853240966797</v>
+        <v>0.005089998245239258</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002256073724572875</v>
+        <v>0.001004552962187728</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0062830448150634766, 0.021465063095092773, 0.007622957229614258, 0.0059719085693359375, 0.00577092170715332, 0.005928754806518555, 0.006413698196411133</t>
+          <t>0.008672714233398438, 0.007194042205810547, 0.0063991546630859375, 0.008219003677368164, 0.0067708492279052734, 0.0064661502838134766, 0.00656580924987793</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0.008493764059884208</v>
+        <v>0.007183960505894252</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.006283044815063477</v>
+        <v>0.006770849227905273</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.00532621220052486</v>
+        <v>0.0008427630829421879</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -1853,31 +1853,31 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.005089759826660156, 0.00453495979309082, 0.004294872283935547, 0.004211902618408203, 0.004590749740600586, 0.004415988922119141, 0.004103899002075195</t>
+          <t>0.0073451995849609375, 0.004645824432373047, 0.004674196243286133, 0.004609107971191406, 0.004503965377807617, 0.0045931339263916016, 0.004388093948364258</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.004463161740984235</v>
+        <v>0.004965645926339286</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004415988922119141</v>
+        <v>0.004609107971191406</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003016161935176782</v>
+        <v>0.0009755660656940003</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.008062124252319336, 0.008096933364868164, 0.008570194244384766, 0.007853984832763672, 0.007461071014404297, 0.007566928863525391, 0.008300065994262695</t>
+          <t>0.01160287857055664, 0.009387969970703125, 0.008130073547363281, 0.009238958358764648, 0.008074045181274414, 0.008416175842285156, 0.009328842163085938</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>0.007987328938075475</v>
+        <v>0.0091684205191476</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.008062124252319336</v>
+        <v>0.009238958358764648</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0003638304503762481</v>
+        <v>0.001124226243386786</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -2243,31 +2243,31 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.005602121353149414, 0.004238128662109375, 0.0036580562591552734, 0.0033910274505615234, 0.003653287887573242, 0.0038139820098876953, 0.003435850143432617</t>
+          <t>0.005604982376098633, 0.0041961669921875, 0.004109859466552734, 0.003693103790283203, 0.003904104232788086, 0.00416874885559082, 0.055033206939697266</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.003970350537981305</v>
+        <v>0.01153002466474261</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003658056259155273</v>
+        <v>0.00416874885559082</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007149619955769531</v>
+        <v>0.01776930614798336</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.007370948791503906, 0.0066907405853271484, 0.006968021392822266, 0.007401943206787109, 0.006975889205932617, 0.007158041000366211, 0.0066602230072021484</t>
+          <t>0.009300947189331055, 0.00962519645690918, 0.0114898681640625, 0.0073621273040771484, 0.007603883743286133, 0.01691126823425293, 0.019090890884399414</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>0.00703225816999163</v>
+        <v>0.01162631171090262</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.006975889205932617</v>
+        <v>0.00962519645690918</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0002750449133673932</v>
+        <v>0.004266887496601929</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -2633,31 +2633,31 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.013518810272216797, 0.012042999267578125, 0.012275934219360352, 0.01221919059753418, 0.012650012969970703, 0.012105941772460938, 0.011887788772583008</t>
+          <t>0.014297008514404297, 0.014793872833251953, 0.01237797737121582, 0.012809991836547852, 0.013186931610107422, 0.012434959411621094, 0.012617111206054688</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.01238581112452916</v>
+        <v>0.01321683611188616</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01221919059753418</v>
+        <v>0.01280999183654785</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0005123054480389144</v>
+        <v>0.0008859957196922687</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.007920265197753906, 0.007838010787963867, 0.007256984710693359, 0.00728607177734375, 0.00757288932800293, 0.007517337799072266, 0.0069272518157958984</t>
+          <t>0.007470846176147461, 0.007607936859130859, 0.007752895355224609, 0.008597135543823242, 0.007718086242675781, 0.0077860355377197266, 0.007859945297241211</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>0.007474115916660854</v>
+        <v>0.007827554430280412</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.007517337799072266</v>
+        <v>0.007752895355224609</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0003217496542431411</v>
+        <v>0.0003355290055023129</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -3023,31 +3023,31 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.011702775955200195, 0.009884834289550781, 0.010586023330688477, 0.010392189025878906, 0.010663986206054688, 0.010020017623901367, 0.010879993438720703</t>
+          <t>0.012148857116699219, 0.010150909423828125, 0.010843992233276367, 0.010285139083862305, 0.010724782943725586, 0.01074981689453125, 0.011121273040771484</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.01058997426714216</v>
+        <v>0.01086068153381348</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01058602333068848</v>
+        <v>0.01074981689453125</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0005592244704769806</v>
+        <v>0.0006086715925960631</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.006797075271606445, 0.006165981292724609, 0.006516933441162109, 0.006468772888183594, 0.007037162780761719, 0.0063991546630859375, 0.006542205810546875</t>
+          <t>0.007092952728271484, 0.00698399543762207, 0.0067901611328125, 0.0066831111907958984, 0.006726264953613281, 0.006674289703369141, 0.0069158077239990234</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0.006561040878295898</v>
+        <v>0.006838083267211914</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.006516933441162109</v>
+        <v>0.0067901611328125</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0002606303160326355</v>
+        <v>0.0001502067323409855</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -3413,31 +3413,31 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.656606912612915, 0.6931262016296387, 0.63690185546875, 0.6366751194000244, 0.6457068920135498, 0.6470780372619629, 0.639066219329834</t>
+          <t>0.7405400276184082, 0.8228521347045898, 0.8180508613586426, 0.7622458934783936, 0.7943110466003418, 0.7523829936981201, 0.8533389568328857</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.6507373196738107</v>
+        <v>0.7919602734701974</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6457068920135498</v>
+        <v>0.7943110466003418</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01849843666946497</v>
+        <v>0.03873212381851463</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.007891178131103516, 0.008076667785644531, 0.007841110229492188, 0.007462978363037109, 0.007193803787231445, 0.007281064987182617, 0.008496761322021484</t>
+          <t>0.0075299739837646484, 0.008975744247436523, 0.009743213653564453, 0.008033990859985352, 0.007512807846069336, 0.007661104202270508, 0.008344173431396484</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0.007749080657958984</v>
+        <v>0.008257286889212472</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.007841110229492188</v>
+        <v>0.008033990859985352</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0004316457591864683</v>
+        <v>0.0007764605239532914</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -3718,6 +3718,3516 @@
       </c>
       <c r="DH8" t="n">
         <v>0.0002243620806489561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9854545454545455</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9932659932659933</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9998258042039252</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.9914458525345622</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9908256880733946</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.9953917050691244</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.793179988861084, 0.7934577465057373, 0.8289229869842529, 0.7861411571502686, 0.7560877799987793, 0.792015790939331, 0.7635347843170166</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.7876200335366386</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.7920157909393311</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.02193111931568551</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.007947921752929688, 0.007160186767578125, 0.00904393196105957, 0.0071871280670166016, 0.00747227668762207, 0.00908207893371582, 0.00846099853515625</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.008050646100725447</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.007947921752929688</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0007655534224082327</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.9622641509433962, 0.9433962264150944, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.8743589743589744, 0.8745421245421245, 0.88003663003663, 0.8772893772893773, 0.9285714285714286, 0.9157509157509157, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.8984563055991629</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.88003663003663</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02607961172524965</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.9166916242387941</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.03609351621237702</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.8275862068965518, 0.7647058823529412, 0.8461538461538461, 0.7999999999999999, 0.923076923076923, 0.888888888888889, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.9367088607594937, 0.8888888888888888, 0.9500000000000001, 0.9210526315789475, 0.975, 0.9620253164556962, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.9421020941031409</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.02726588893481355</v>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.8821475338280227, 0.826797385620915, 0.8980769230769231, 0.8605263157894737, 0.9490384615384615, 0.9254571026722926, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.8958341521592192</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.8980769230769231</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.03964076147827795</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.8495662102152975</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.0525229007147746</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.65, 0.9166666666666666, 0.75, 1.0, 0.9230769230769231, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.925, 0.9696969696969697, 0.926829268292683, 0.9459459459459459, 0.9512195121951219, 0.95, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.9489108438081482</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.01740449033663503</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.8519361590790163</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.1086194131115752</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.8, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8205128205128205, 0.9743589743589743, 0.8974358974358975, 1.0, 0.9743589743589743, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.9377289377289377</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.05627213002101544</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.8591836734693877</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.05146742944048364</v>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0.9692307692307692, 0.9084249084249084, 0.9853479853479854, 0.9304029304029304, 0.9945054945054945, 0.9120879120879121, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.9553113553113554</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.9692307692307692</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0345061944354013</v>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9937304075235109, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0.9919108669108669, 1.0, 0.9919808949220714, 0.9941176470588236, 0.9978632478632479, 0.9978632478632479, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.9951023999343328</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.9941176470588236</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.003159436146015735</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.00219678391174473</v>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 0.9940828402366864, 0.9941520467836257, 0.9941520467836257, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 0.9957264957264957, 0.9978678038379531, 0.9978586723768736, 0.9978586723768736, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.9972520908244553</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.9978586723768736</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.001495149821458733</v>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>0.9919108669108669, 1.0, 0.9919808949220714, 0.9959753220373198, 0.9960053595802496, 0.9960053595802496, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.994836956850404</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.9959753220373198</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.002817278361235357</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.9924218228763528</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.9940828402366864</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.004139504433597427</v>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 1.0, 0.9883720930232558, 0.9883720930232558, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 0.9957264957264957, 0.9957446808510638, 1.0, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.9975605954329358</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.9957446808510638</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.002112594711100439</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.9916157160538634</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.9883720930232558</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.005303407062568835</v>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 0.9882352941176471, 0.9882352941176471, 1.0, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 0.9957264957264957, 1.0, 0.9957264957264957, 0.9957264957264957, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.996947496947497</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.001930572442105231</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.9932573029211685</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.005839526916084106</v>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>0.9998982498982498, 1.0, 0.9999497234791352, 1.0, 1.0, 1.0, 0.9999497234791352</t>
+        </is>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.9999710995509314</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>3.695922195409029e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9471450617283951</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8528257456828885</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.25836896896362305, 0.24454593658447266, 0.24982810020446777, 0.23743414878845215, 0.3201718330383301, 0.2678191661834717, 0.26900601387023926</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2638820239475795</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.258368968963623</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.02538722933165448</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.008426189422607422, 0.009593009948730469, 0.008414983749389648, 0.008800983428955078, 0.008508920669555664, 0.009994983673095703, 0.008940696716308594</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.008954252515520369</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.008800983428955078</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.0005710628510154612</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.7924528301886793, 0.9245283018867925, 0.8301886792452831, 0.9056603773584906, 0.8301886792452831, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8023809523809524, 0.9295665634674922, 0.8328173374613003, 0.903250773993808, 0.8560371517027863, 0.8390092879256965</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.8729186411406668</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.8560371517027863</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.05027112793891122</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.8734151941699111</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.05605255122691098</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8307692307692307, 0.9393939393939394, 0.8615384615384616, 0.9253731343283583, 0.8524590163934426, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7317073170731708, 0.9, 0.7804878048780488, 0.8717948717948718, 0.7999999999999999, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.8326334911700766</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.06929100562647317</v>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.7812382739212007, 0.9196969696969697, 0.8210131332082552, 0.898584003061615, 0.8262295081967213, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.8651142066814581</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.8507042253521127</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.05792736212327599</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.89759492219284</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.9014084507042254</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.04766783161975097</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9, 0.96875, 0.9032258064516129, 0.9393939393939394, 0.9629629629629629, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1.0, 0.6521739130434783, 0.8571428571428571, 0.7272727272727273, 0.85, 0.6923076923076923, 0.875</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.8076995985381078</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.1132095154495363</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.9264490742313323</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.0352578632957699</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.9117647058823529, 0.8235294117647058, 0.9117647058823529, 0.7647058823529411, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.8421052631578947, 0.8947368421052632, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.8709273182957393</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.06870551459585363</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.8749099639855943</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.08302203697858708</v>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0.9894736842105264, 0.946031746031746, 0.9752321981424148, 0.9489164086687307, 0.9442724458204335, 0.9303405572755418, 0.93343653250774</t>
+        </is>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.9525290818081619</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.946031746031746</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.02021537609599209</v>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>0.9999784157133608, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>9.712984233443494e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 8, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9818181818181818</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8825240545983442</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8886363636363637</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9357798165137615</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.22781109809875488, 0.24125099182128906, 0.2810487747192383, 0.24719500541687012, 0.24962806701660156, 0.2490081787109375, 0.3338658809661865</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2614011423928397</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.2490081787109375</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.03309184754304973</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.00776982307434082, 0.008003950119018555, 0.007461071014404297, 0.007875919342041016, 0.007687091827392578, 0.00847482681274414, 0.01051020622253418</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.008254698344639369</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.007875919342041016</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.0009657895408599467</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.9056603773584906, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.8410256410256409, 0.8287545787545787, 0.8672161172161172, 0.8388278388278387, 0.9157509157509157, 0.8672161172161172, 0.9615384615384616</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.8743328100470958</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.04451151604293877</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.8951781970649896</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.04010718337465197</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0.7857142857142856, 0.7333333333333334, 0.8148148148148148, 0.7272727272727273, 0.888888888888889, 0.8148148148148148, 0.9032258064516129</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.9249999999999999, 0.8947368421052632, 0.9367088607594937, 0.8767123287671232, 0.9620253164556962, 0.9367088607594937, 0.9600000000000001</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.9274131726924385</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.9367088607594937</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.02946393194827078</v>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.8553571428571427, 0.8140350877192983, 0.8757618377871542, 0.8019925280199253, 0.9254571026722926, 0.8757618377871542, 0.9316129032258065</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.8685683485812534</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.04612899795543637</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.8097235244700682</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.06355168081410603</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.6875, 0.8461538461538461, 0.631578947368421, 0.9230769230769231, 0.8461538461538461, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.918918918918919, 0.925, 0.9411764705882353, 0.95, 0.925, 1.0</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.9375049162710569</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.02918670159910827</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.8005924029530841</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.09495227307681021</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8717948717948718, 0.9487179487179487, 0.8205128205128205, 0.9743589743589743, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.9194139194139195</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.05022457582711388</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.8292517006802721</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.08070906095218444</v>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.976068376068376, 0.9102564102564101, 0.9761904761904762, 0.9340659340659341, 0.9963369963369964, 0.923076923076923, 0.9926739926739927</t>
+        </is>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.9583813012384441</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.976068376068376</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.0325143136281283</v>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_splashing_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 10, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8591820987654321</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.784688995215311</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.787037037037037</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9427609427609428</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.9553805774278215</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9932539682539682</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9377841854275257</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.940625</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.9074074074074074</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9201877934272301</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.04421710968017578, 0.03908491134643555, 0.03708004951477051, 0.10230708122253418, 0.034369707107543945, 0.03495287895202637, 0.03665900230407715</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.04695296287536621</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.03708004951477051</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.02280115889258556</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.010421991348266602, 0.011258840560913086, 0.018460750579833984, 0.011870861053466797, 0.010409355163574219, 0.012333869934082031, 0.011394023895263672</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.01230709893362863</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.01139402389526367</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.002595217095907184</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8301886792452831, 0.8490566037735849, 0.7924528301886793, 0.9056603773584906, 0.8113207547169812, 0.7547169811320755</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.8174603174603174, 0.8243034055727554, 0.7801857585139318, 0.903250773993808, 0.8297213622291022, 0.7275541795665634</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.8215566928525794</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.8243034055727554</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.05279232137251848</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.8358290905460716</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.05246492459552389</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8695652173913043, 0.8857142857142858, 0.8358208955223881, 0.9253731343283583, 0.8387096774193549, 0.8115942028985507</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.8484848484848484, 0.7567567567567567, 0.7777777777777778, 0.717948717948718, 0.8717948717948718, 0.7727272727272727, 0.6486486486486486</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.7705912705912705</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.06989627205704758</v>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.8909090909090909, 0.8131609870740305, 0.8317460317460318, 0.776884806735553, 0.898584003061615, 0.8057184750733137, 0.7301214257735996</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.8210178314818907</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.8131609870740305</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.05544891362232967</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.8714443923725108</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.04287582010502988</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.875, 0.8823529411764706, 0.8611111111111112, 0.8484848484848485, 0.9393939393939394, 0.9285714285714286, 0.8</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>1.0, 0.7368421052631579, 0.8235294117647058, 0.7, 0.85, 0.68, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.7795768833849329</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.1110344893763404</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.8764163241053998</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.04404130498007724</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9117647058823529, 0.8235294117647058, 0.9117647058823529, 0.7647058823529411, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.7777777777777778, 0.7368421052631579, 0.7368421052631579, 0.8947368421052632, 0.8947368421052632, 0.631578947368421</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.772765246449457</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.08749224702814402</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.8703481392557022</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.07167278960035725</v>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0.9383458646616541, 0.8873015873015874, 0.913312693498452, 0.9024767801857586, 0.9427244582043344, 0.8119195046439629, 0.8622291021671827</t>
+        </is>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.8940442843804188</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.9024767801857586</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.04238752704731504</v>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>0.9182389937106918, 0.9216300940438872, 0.9090909090909091, 0.9341692789968652, 0.9278996865203761, 0.9592476489028213, 0.9028213166144201</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0.9167278221454781, 0.9215019255455712, 0.9076381132399691, 0.929053183263167, 0.9301915972162558, 0.958458630466535, 0.8987885557178452</t>
+        </is>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.9231942610849746</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.9215019255455712</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.0177650397140095</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.9247282754114244</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.9216300940438872</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.01718358484681609</v>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>0.9356435643564357, 0.9379652605459058, 0.928395061728395, 0.9489051094890512, 0.9429280397022333, 0.9682151589242055, 0.9238329238329238</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>0.8879310344827587, 0.8936170212765957, 0.8755364806866952, 0.9074889867841409, 0.902127659574468, 0.943231441048035, 0.8658008658008658</t>
+        </is>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.8965333556647943</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.02329896654968231</v>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>0.9117872994195972, 0.9157911409112507, 0.9019657712075451, 0.928197048136596, 0.9225278496383507, 0.9557232999861203, 0.8948168948168949</t>
+        </is>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.9186870434451935</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.9157911409112507</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.01844781806647643</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.9408407312255929</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.9379652605459058</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.01361820956301094</v>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>0.949748743718593, 0.9545454545454546, 0.9447236180904522, 0.9512195121951219, 0.9644670050761421, 0.9753694581280788, 0.9353233830845771</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>0.865546218487395, 0.8677685950413223, 0.85, 0.9035087719298246, 0.8688524590163934, 0.9310344827586207, 0.847457627118644</t>
+        </is>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.8763097363360287</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.8677685950413223</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.02803988800856164</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.9536281678340599</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.01210792665768993</v>
+      </c>
+      <c r="CW12" t="inlineStr">
+        <is>
+          <t>0.9219512195121952, 0.9219512195121952, 0.912621359223301, 0.9466019417475728, 0.9223300970873787, 0.9611650485436893, 0.912621359223301</t>
+        </is>
+      </c>
+      <c r="CX12" t="inlineStr">
+        <is>
+          <t>0.911504424778761, 0.9210526315789473, 0.9026548672566371, 0.911504424778761, 0.9380530973451328, 0.9557522123893806, 0.8849557522123894</t>
+        </is>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.9179253443342869</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.911504424778761</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.02154203931311345</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.9284631778356618</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0.9219512195121952</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0.01699907316729176</v>
+      </c>
+      <c r="DE12" t="inlineStr">
+        <is>
+          <t>0.9798834448521476, 0.9839109970047069, 0.9804966062376492, 0.9862316350201907, 0.9817638972420311, 0.9926110490591975, 0.981248389036859</t>
+        </is>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.9837351454932545</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.9817638972420311</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.004147952326222077</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_no_fragmentation_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 6, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9490909090909091</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8532927624429472</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8704545454545454</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8909090909090909</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.9158878504672897</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.9730639730639731</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9176470588235294</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.9958193008942051</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9663074305161656</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.9776158402043897</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.9952830188679245</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.9678899082568807</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.9813953488372092</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.06338882446289062, 0.032479047775268555, 0.032704830169677734, 0.03319716453552246, 0.033941030502319336, 0.03191208839416504, 0.03241300582885742</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.03714799880981445</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.03270483016967773</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.01072946833912126</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.040789127349853516, 0.010082721710205078, 0.009205102920532227, 0.00997304916381836, 0.009591102600097656, 0.013094186782836914, 0.009294986724853516</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.01457575389317104</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.009973049163818359</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.01077222195128435</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.8301886792452831, 0.9245283018867925, 0.8301886792452831, 0.8867924528301887, 0.9056603773584906, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.7897435897435897, 0.8388278388278387, 0.88003663003663, 0.8388278388278387, 0.8543956043956045, 0.8672161172161172, 0.9029304029304028</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.8531397174254316</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.03344720209792343</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.8738145153239492</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.04410013588092931</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.6875, 0.7272727272727273, 0.8461538461538461, 0.7272727272727273, 0.7857142857142857, 0.8148148148148148, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.8767123287671232, 0.9500000000000001, 0.8767123287671232, 0.9230769230769231, 0.9367088607594937, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.9114784918171701</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.03362204660054285</v>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.7779605263157895, 0.8019925280199253, 0.8980769230769231, 0.8019925280199253, 0.8543956043956045, 0.8757618377871542, 0.9029304029304028</t>
+        </is>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.8447300500779608</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.0469052625837614</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.7779816083387512</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.06054530700835218</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.6470588235294118, 0.631578947368421, 0.9166666666666666, 0.631578947368421, 0.7857142857142857, 0.8461538461538461, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.9411764705882353, 0.926829268292683, 0.9411764705882353, 0.9230769230769231, 0.925, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.928266996165131</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.01737969223386602</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.759413481991987</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.1119962522792415</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8205128205128205, 0.9743589743589743, 0.8205128205128205, 0.9230769230769231, 0.9487179487179487, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.8974358974358976</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.06129377483766121</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.808843537414966</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.04520611626077863</v>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>0.8615384615384615, 0.9084249084249084, 0.9816849816849818, 0.9258241758241759, 0.9285714285714286, 0.923992673992674, 0.9780219780219781</t>
+        </is>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.929722658294087</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.9258241758241759</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.03814435436712547</v>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>0.9779874213836478, 0.9655172413793104, 0.9592476489028213, 0.9811912225705329, 0.9623824451410659, 0.9655172413793104, 0.9435736677115988</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>0.9774114774114774, 0.9652589240824535, 0.9609854198089492, 0.9796882855706385, 0.959376571141277, 0.9652589240824535, 0.9428104575163399</t>
+        </is>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.9643985799447984</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.9652589240824535</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.01138613346635316</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.9650595554954696</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.01152864695153742</v>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>0.95906432748538, 0.9371428571428572, 0.9265536723163841, 0.9651162790697674, 0.9310344827586207, 0.9371428571428572, 0.898876404494382</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>0.9849462365591398, 0.9762419006479482, 0.9718004338394794, 0.9871244635193134, 0.9741379310344828, 0.9762419006479482, 0.9608695652173912</t>
+        </is>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.9759089187808146</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.9762419006479482</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.008052342267687191</v>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>0.9720052820222599, 0.9566923788954027, 0.9491770530779318, 0.9761203712945403, 0.9525862068965517, 0.9566923788954027, 0.9298729848558867</t>
+        </is>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.9561638079911395</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.9566923788954027</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.01415524560871515</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.9364186972014641</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.9371428571428572</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.02025958966633972</v>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>0.9425287356321839, 0.9111111111111111, 0.8913043478260869, 0.9540229885057471, 0.9101123595505618, 0.9111111111111111, 0.8602150537634409</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>0.9913419913419913, 0.9868995633187773, 0.986784140969163, 0.9913793103448276, 0.9826086956521739, 0.9868995633187773, 0.9778761061946902</t>
+        </is>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.9862556244486288</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.9868995633187773</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.004419895690442677</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.9114865296428919</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.9111111111111111</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.02881275463750477</v>
+      </c>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9647058823529412, 0.9647058823529412, 0.9764705882352941, 0.9529411764705882, 0.9647058823529412, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="CX13" t="inlineStr">
+        <is>
+          <t>0.9786324786324786, 0.9658119658119658, 0.9572649572649573, 0.9829059829059829, 0.9658119658119658, 0.9658119658119658, 0.9444444444444444</t>
+        </is>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.9658119658119658</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.9658119658119658</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.01186948845862244</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.9629851940776311</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.01159815469077017</v>
+      </c>
+      <c r="DE13" t="inlineStr">
+        <is>
+          <t>0.9979649979649979, 0.9974358974358974, 0.9936400201106084, 0.9979135243841126, 0.993815987933635, 0.9961287078934138, 0.9934640522875816</t>
+        </is>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.9957661697157495</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.9961287078934138</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.001926835603890327</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_splashing_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9533179012345678</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.08466815948486328, 0.07819819450378418, 0.07041501998901367, 0.06761980056762695, 0.07537388801574707, 0.06524491310119629, 0.07358479499816895</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.07358639580862862</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.07358479499816895</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.006123812088318267</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.013681888580322266, 0.011255979537963867, 0.011024951934814453, 0.010769128799438477, 0.012682914733886719, 0.010698080062866211, 0.012078046798706055</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.01174157006399972</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.01125597953796387</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.001038407807507469</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8867924528301887, 0.8867924528301887, 0.8490566037735849, 0.9622641509433962, 0.8113207547169812, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.8738095238095238, 0.8769349845201238, 0.8475232198142415, 0.9473684210526316, 0.8297213622291022, 0.8243034055727554</t>
+        </is>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.8743876497967608</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.8738095238095238</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.04265449734207535</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.8842467804731956</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.05002618177810771</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.9142857142857143, 0.9117647058823528, 0.8787878787878787, 0.9714285714285714, 0.8387096774193549, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.9142857142857143, 0.8333333333333334, 0.8421052631578947, 0.8, 0.9444444444444444, 0.7727272727272727, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.8406676865323481</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.06149330978186609</v>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.9365949119373776, 0.8738095238095238, 0.8769349845201238, 0.8393939393939394, 0.9579365079365079, 0.8057184750733137, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.8745906249166883</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.8738095238095238</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.05156828043059845</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.9085135633010285</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.9117647058823528</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.04279085169319258</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.9142857142857143, 0.9117647058823529, 0.90625, 0.9444444444444444, 0.9285714285714286, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>1.0, 0.8333333333333334, 0.8421052631578947, 0.7619047619047619, 1.0, 0.68, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.8486961100229565</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.1086867495936684</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.9124971479819999</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.02401040141082343</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>1.0, 0.9142857142857143, 0.9117647058823529, 0.8529411764705882, 1.0, 0.7647058823529411, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8333333333333334, 0.8421052631578947, 0.8421052631578947, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.8408521303258144</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.04882395924505805</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.907923169267707</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0761206684010938</v>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>0.9969924812030075, 0.946031746031746, 0.976780185758514, 0.9342105263157895, 0.9512383900928792, 0.9195046439628484, 0.9411764705882354</t>
+        </is>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.9522763491361458</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.946031746031746</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.02438854772535699</v>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO14" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP14" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX14" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>9.712984233453662e-06</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_no_fragmentation_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 8, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9777272727272727</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8858943707889591</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9045454545454545</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9345794392523366</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.10165286064147949, 0.07521605491638184, 0.0776362419128418, 0.07327508926391602, 0.07524776458740234, 0.07541704177856445, 0.0753777027130127</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.0791175365447998</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.0753777027130127</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.009273972555047529</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.012701988220214844, 0.011260986328125, 0.011708974838256836, 0.010669946670532227, 0.01034402847290039, 0.009556055068969727, 0.011501073837280273</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.01110615049089704</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.011260986328125</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.0009459638620693968</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.8113207547169812, 0.9056603773584906, 0.8113207547169812, 0.9433962264150944, 0.9056603773584906, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.782051282051282, 0.7802197802197802, 0.8672161172161172, 0.8031135531135531, 0.9386446886446886, 0.8901098901098901, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.8553113553113555</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.06210539109258142</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.8764600179694518</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.05188241659008128</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.689655172413793, 0.6666666666666666, 0.8148148148148148, 0.6875000000000001, 0.896551724137931, 0.8275862068965518, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.8860759493670887, 0.868421052631579, 0.9367088607594937, 0.8648648648648648, 0.9610389610389611, 0.935064935064935, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.9142204349685078</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.935064935064935</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.03694910328727866</v>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.7878655608904408, 0.7675438596491229, 0.8757618377871542, 0.7761824324324325, 0.9287953425884461, 0.8813255709807435, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.8463560211697126</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.06224428467103883</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.7784916073709177</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.08792764030382219</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.7142857142857143, 0.625, 0.8461538461538461, 0.6111111111111112, 0.8666666666666667, 0.8, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.875, 0.8918918918918919, 0.925, 0.9142857142857143, 0.9736842105263158, 0.9473684210526315, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.9286004586756466</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.03544030065368339</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.7536739054596199</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.09662820782542658</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.8461538461538461, 0.9487179487179487, 0.8205128205128205, 0.9487179487179487, 0.9230769230769231, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.9010989010989012</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.04633373861052571</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.8095238095238094</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.09352195295828246</v>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>0.9324786324786324, 0.8763736263736264, 0.9752747252747253, 0.9130036630036629, 0.9945054945054945, 0.9313186813186813, 0.989010989010989</t>
+        </is>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.9445665445665447</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.9324786324786324</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.04032070154024791</v>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_splashing_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 10, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9506172839506173</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.863608809860578</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.849537037037037</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0.46227097511291504, 0.48512792587280273, 0.4832901954650879, 0.4716978073120117, 0.45341992378234863, 0.5346879959106445, 0.48238706588745117</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.4818402699061802</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.4823870658874512</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.02420045753861314</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>0.01100921630859375, 0.012105941772460938, 0.010255813598632812, 0.010008096694946289, 0.009479999542236328, 0.009672880172729492, 0.009705066680908203</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.01031957353864397</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.01000809669494629</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.0008675513368268544</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8301886792452831, 0.9433962264150944, 0.8679245283018868, 0.9056603773584906, 0.8679245283018868, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.830952380952381, 0.9326625386996904, 0.8854489164086687, 0.903250773993808, 0.8854489164086687, 0.8885448916408669</t>
+        </is>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.8962395484509594</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.8885448916408669</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.03493759861513632</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.8949785364879705</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.04277655056961074</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8656716417910447, 0.9565217391304348, 0.888888888888889, 0.9253731343283583, 0.888888888888889, 0.9090909090909091</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7692307692307692, 0.918918918918919, 0.8372093023255814, 0.8717948717948718, 0.8372093023255814, 0.8500000000000001</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.8612582298628809</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.0535966753545923</v>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8174512055109069, 0.937720329024677, 0.8630490956072352, 0.898584003061615, 0.8630490956072352, 0.8795454545454546</t>
+        </is>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.888247502384351</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.8795454545454546</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.04443966731526079</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.9152367749058211</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.03573200154652034</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.90625, 0.9428571428571428, 0.9655172413793104, 0.9393939393939394, 0.9655172413793104, 0.9375</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>1.0, 0.7142857142857143, 0.9444444444444444, 0.75, 0.85, 0.75, 0.8095238095238095</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.8311791383219954</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.09928089198165066</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.9432830729936642</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.01857804612671459</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>1.0, 0.8285714285714286, 0.9705882352941176, 0.8235294117647058, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8947368421052632, 0.9473684210526315, 0.8947368421052632, 0.9473684210526315, 0.8947368421052632</t>
+        </is>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.9010025062656641</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.03592799796198356</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.8914765906362546</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.067317508811085</v>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>0.9924812030075187, 0.9365079365079365, 0.9876160990712075, 0.9705882352941176, 0.958204334365325, 0.9125386996904025, 0.9380804953560371</t>
+        </is>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.9565738576132208</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.958204334365325</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.02708652858338519</v>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO16" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP16" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY16" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF16" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>9.712984233463661e-06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_no_fragmentation_smote_grid-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.980909090909091</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8858943707889591</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.9045454545454545</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9345794392523366</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>0.57930588722229, 0.5847277641296387, 0.49130702018737793, 0.4850151538848877, 0.4905588626861572, 0.5041279792785645, 0.5337998867034912</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.5241203648703439</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.5041279792785645</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.03954092796649499</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>0.00900721549987793, 0.00811314582824707, 0.008222103118896484, 0.008510828018188477, 0.008167028427124023, 0.008897781372070312, 0.008836984634399414</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.008536440985543388</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.008510828018188477</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.000350026682689712</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8679245283018868, 0.9056603773584906, 0.8679245283018868, 0.9433962264150944, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.8644688644688645, 0.8672161172161172, 0.8644688644688645, 0.9157509157509157, 0.9029304029304028, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.8819989534275249</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.03093646373846525</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.9059099530797645</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.9074074074074074</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.02669027688607385</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>0.8, 0.7741935483870968, 0.8148148148148148, 0.7741935483870968, 0.888888888888889, 0.8571428571428571, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>0.9397590361445783, 0.9066666666666667, 0.9367088607594937, 0.9066666666666667, 0.9620253164556962, 0.9487179487179487, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.9354161309233833</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.9397590361445783</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.01964484562333443</v>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.8698795180722891, 0.8404301075268817, 0.8757618377871542, 0.8404301075268817, 0.9254571026722926, 0.9029304029304028, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.8802723743393643</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.03064431636352031</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.8251286177553459</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.04266527150878797</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>1.0, 0.7058823529411765, 0.8461538461538461, 0.7058823529411765, 0.9230769230769231, 0.8571428571428571, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>0.8863636363636364, 0.9444444444444444, 0.925, 0.9444444444444444, 0.95, 0.9487179487179487, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.938849063849064</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.02505796900711914</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.8358054760365684</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0.09960041652786275</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>1.0, 0.8717948717948718, 0.9487179487179487, 0.8717948717948718, 0.9743589743589743, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.9340659340659341</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.04516054214629286</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.8299319727891156</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.07681353599072255</v>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>0.958974358974359, 0.9157509157509158, 0.9835164835164836, 0.9377289377289377, 0.9835164835164836, 0.9065934065934067, 0.9908424908424909</t>
+        </is>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.9538461538461539</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.958974358974359</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0.03184677222556585</v>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4_smote_mean_opt.xlsx
+++ b/results/metrics_modelling4_smote_mean_opt.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH17"/>
+  <dimension ref="A1:DH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7228,6 +7228,6246 @@
       </c>
       <c r="DH17" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 8, 'sampling_strategy': 0.78}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8850308641975309</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.793956043956044</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7893518518518519</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.7307692307692308</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8451178451178452</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.9195402298850575</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8743169398907105</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.9171378968253969</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.8362812769628991</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.7398373983739838</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.7982456140350878</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.008255958557128906, 0.00521397590637207, 0.005760908126831055, 0.0052568912506103516, 0.005004167556762695, 0.005067110061645508, 0.0056269168853759766</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.005740846906389509</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.005256891250610352</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.001058812882800558</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.007971763610839844, 0.008599042892456055, 0.006973981857299805, 0.006758928298950195, 0.006936788558959961, 0.00700688362121582, 0.006643056869506836</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.00727006367274693</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.006973981857299805</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.0006741095665104198</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8113207547169812, 0.8301886792452831, 0.7735849056603774, 0.8301886792452831, 0.7547169811320755, 0.7358490566037735</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.8166666666666667, 0.8328173374613003, 0.7770897832817337, 0.8212074303405572, 0.7739938080495357, 0.7128482972136223</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.8076314736420885</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.8166666666666667</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.05892632150019866</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.8088249975042426</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.05870835848929566</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8484848484848486, 0.8615384615384616, 0.8125, 0.8656716417910447, 0.7868852459016393, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7499999999999999, 0.7804878048780488, 0.7142857142857143, 0.7692307692307692, 0.7111111111111111, 0.631578947368421</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.7502044555684754</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.7499999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.07469862416881945</v>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7992424242424243, 0.8210131332082552, 0.7633928571428572, 0.8174512055109069, 0.7489981785063753, 0.7128482972136223</t>
+        </is>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.7973918697579493</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.7992424242424243</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.06135199063425347</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.844579283947423</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.8484848484848486</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.04972833560210224</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.9032258064516129, 0.9032258064516129, 0.8666666666666667, 0.8787878787878788, 0.8888888888888888, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6818181818181818, 0.7272727272727273, 0.6521739130434783, 0.75, 0.6153846153846154, 0.631578947368421</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.7075664609989553</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.08882132696315838</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.8825385481660895</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.04245808840875637</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8235294117647058, 0.7647058823529411, 0.8529411764705882, 0.7058823529411765, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8421052631578947, 0.7894736842105263, 0.7894736842105263, 0.8421052631578947, 0.631578947368421</t>
+        </is>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.8032581453634087</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.07759311067876051</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.8120048019207682</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.06855046740466811</v>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>0.9548872180451128, 0.8666666666666667, 0.9458204334365325, 0.8699690402476781, 0.9380804953560372, 0.8452012383900929, 0.871517027863777</t>
+        </is>
+      </c>
+      <c r="BR18" t="n">
+        <v>0.8988774457151283</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.871517027863777</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.04205536433457384</v>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>0.8113207547169812, 0.8338557993730408, 0.8244514106583072, 0.8275862068965517, 0.8338557993730408, 0.8401253918495298, 0.8369905956112853</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>0.8179149579106411, 0.8395806589644843, 0.8301185668871895, 0.8245553741730389, 0.8374001202852479, 0.8462496778073718, 0.8338345218661396</t>
+        </is>
+      </c>
+      <c r="BW18" t="n">
+        <v>0.8328076968420162</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0.8338345218661396</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.008830390002084841</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.8297408512112481</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.8338557993730408</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0.008993519120745716</v>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>0.8445595854922281, 0.8637532133676091, 0.8564102564102564, 0.8621553884711779, 0.8651399491094147, 0.8695652173913043, 0.87</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>0.76, 0.7871485943775101, 0.7741935483870968, 0.7698744769874477, 0.7836734693877551, 0.7935222672064777, 0.7815126050420168</t>
+        </is>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.7785607087697578</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.7815126050420168</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.01049814027902088</v>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>0.802279792746114, 0.8254509038725596, 0.8153019023986765, 0.8160149327293128, 0.824406709248585, 0.8315437422988909, 0.8257563025210084</t>
+        </is>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.8201077551164496</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.8244067092485849</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.009003188273323031</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0.8616548014631416</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.8637532133676091</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.008183335459245227</v>
+      </c>
+      <c r="CO18" t="inlineStr">
+        <is>
+          <t>0.9005524861878453, 0.9130434782608695, 0.907608695652174, 0.8911917098445595, 0.9090909090909091, 0.918918918918919, 0.8969072164948454</t>
+        </is>
+      </c>
+      <c r="CP18" t="inlineStr">
+        <is>
+          <t>0.6934306569343066, 0.725925925925926, 0.7111111111111111, 0.7301587301587301, 0.7272727272727273, 0.7313432835820896, 0.744</t>
+        </is>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0.7233203478549843</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0.01513580621477926</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0.9053304877785889</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0.9076086956521739</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0.008921503095532258</v>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>0.7951219512195122, 0.8195121951219512, 0.8106796116504854, 0.8349514563106796, 0.8252427184466019, 0.8252427184466019, 0.8446601941747572</t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr">
+        <is>
+          <t>0.8407079646017699, 0.8596491228070176, 0.8495575221238938, 0.8141592920353983, 0.8495575221238938, 0.8672566371681416, 0.8230088495575221</t>
+        </is>
+      </c>
+      <c r="CY18" t="n">
+        <v>0.8434138443453767</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0.8495575221238938</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0.01767591993138566</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0.8222015493386557</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0.8252427184466019</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0.01492237334265455</v>
+      </c>
+      <c r="DE18" t="inlineStr">
+        <is>
+          <t>0.9025037772501618, 0.9157466837826274, 0.9044376664661913, 0.9144471174499527, 0.9052538877910474, 0.918549703582782, 0.9123850846292636</t>
+        </is>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.9104748458502895</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0.9123850846292636</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0.005851342080962566</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.64}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7346938775510204</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8029905031319459</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8712871287128713</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6371681415929203</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.7499999999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.9451863895018</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.8152985074626865</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.8616595052839391</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9619565217391305</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.8119266055045872</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8805970149253731</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0.004731893539428711, 0.007187366485595703, 0.007794857025146484, 0.0051958560943603516, 0.004901885986328125, 0.004445075988769531, 0.0057790279388427734</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.005719423294067383</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.005195856094360352</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.001195676797723801</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0.00828099250793457, 0.008136987686157227, 0.007276058197021484, 0.00838613510131836, 0.006907939910888672, 0.0077669620513916016, 0.006531953811645508</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.007612432752336774</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.007766962051391602</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.0006677806954894768</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7169811320754716, 0.8490566037735849, 0.8113207547169812, 0.8301886792452831, 0.8679245283018868, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>0.8692307692307693, 0.739010989010989, 0.8745421245421245, 0.848901098901099, 0.8617216117216118, 0.8644688644688645, 0.8974358974358974</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.8507587650444793</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.8644688644688645</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.04763669807041433</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.8278426674653091</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.04911208851918584</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>0.7878787878787877, 0.5945945945945946, 0.7647058823529412, 0.7222222222222223, 0.742857142857143, 0.7741935483870968, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>0.9066666666666667, 0.7826086956521738, 0.8888888888888888, 0.8571428571428572, 0.8732394366197183, 0.9066666666666667, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.8715610710501797</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.8857142857142858</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.03980057310385378</v>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>0.8472727272727272, 0.6886016451233843, 0.826797385620915, 0.7896825396825398, 0.8080482897384307, 0.8404301075268817, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.8046541038158443</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.826797385620915</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.05074362506646927</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.737747136581509</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.7647058823529412</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.06202595656055507</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>0.7222222222222222, 0.4782608695652174, 0.65, 0.5909090909090909, 0.6190476190476191, 0.7058823529411765, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.9, 0.9696969696969697, 0.967741935483871, 0.96875, 0.9444444444444444, 1.0</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.9564396848671043</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.02884874594131466</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.6289551130069946</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.07499403846082844</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7857142857142857, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.6923076923076923, 0.8205128205128205, 0.7692307692307693, 0.7948717948717948, 0.8717948717948718, 0.7948717948717948</t>
+        </is>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.8021978021978021</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.7948717948717948</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.05768503937004989</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.8993197278911564</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.0637571402114829</v>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>0.9555555555555555, 0.8956043956043955, 0.9706959706959707, 0.9322344322344323, 0.9194139194139195, 0.9395604395604396, 0.9963369963369964</t>
+        </is>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.9442002442002443</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.9395604395604396</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0.03091424632787118</v>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>0.8207547169811321, 0.8526645768025078, 0.8338557993730408, 0.8338557993730408, 0.8401253918495298, 0.8369905956112853, 0.8338557993730408</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>0.8400488400488401, 0.8770990447461036, 0.8567873303167421, 0.8530417295123178, 0.8535696329813977, 0.8626696832579186, 0.8492961287078934</t>
+        </is>
+      </c>
+      <c r="BW19" t="n">
+        <v>0.8560731985101732</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0.8535696329813977</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0.01071898308773126</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.8360146684805111</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0.8338557993730408</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0.00879868654763752</v>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>0.7219512195121951, 0.7707317073170731, 0.7439613526570049, 0.7414634146341464, 0.7462686567164178, 0.75, 0.7389162561576355</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>0.8677494199535963, 0.8914549653579676, 0.8770301624129929, 0.8775981524249422, 0.8832951945080091, 0.8790697674418605, 0.8781609195402298</t>
+        </is>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.8791940830913713</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0.8781609195402298</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.006616441553785772</v>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>0.7948503197328958, 0.8310933363375204, 0.8104957575349989, 0.8095307835295443, 0.8147819256122135, 0.8145348837209303, 0.8085385878489326</t>
+        </is>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.8119750849024338</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.8104957575349989</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.009951084474055641</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0.7447560867134962</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0.7439613526570049</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0.01347038148226321</v>
+      </c>
+      <c r="CO19" t="inlineStr">
+        <is>
+          <t>0.6115702479338843, 0.6583333333333333, 0.6311475409836066, 0.6333333333333333, 0.646551724137931, 0.6341463414634146, 0.635593220338983</t>
+        </is>
+      </c>
+      <c r="CP19" t="inlineStr">
+        <is>
+          <t>0.949238578680203, 0.9698492462311558, 0.9593908629441624, 0.9547738693467337, 0.9507389162561576, 0.9642857142857143, 0.9502487562189055</t>
+        </is>
+      </c>
+      <c r="CQ19" t="n">
+        <v>0.9569322777090046</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>0.9547738693467337</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0.007307966921173903</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0.6358108202177838</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0.01331453508883338</v>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9294117647058824, 0.9058823529411765, 0.8941176470588236, 0.8823529411764706, 0.9176470588235294, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr">
+        <is>
+          <t>0.7991452991452992, 0.8247863247863247, 0.8076923076923077, 0.811965811965812, 0.8247863247863247, 0.8076923076923077, 0.8162393162393162</t>
+        </is>
+      </c>
+      <c r="CY19" t="n">
+        <v>0.8131868131868131</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0.811965811965812</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0.00876233216996781</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0.8989595838335335</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0.01782352635268402</v>
+      </c>
+      <c r="DE19" t="inlineStr">
+        <is>
+          <t>0.9458689458689459, 0.9543991955756662, 0.9431875314228254, 0.9490698843640021, 0.9471593765711412, 0.9498240321769733, 0.9369029663147311</t>
+        </is>
+      </c>
+      <c r="DF19" t="n">
+        <v>0.9466302760420408</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0.9471593765711412</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0.005124736840357996</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 9, 'sampling_strategy': 0.95}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8912037037037037</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8290273556231003</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8344907407407407</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.9023569023569024</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9657142857142857</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8802083333333334</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9209809264305177</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.8966138112328801</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.911532738095238</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8114754098360656</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.8722466960352424</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>0.005599021911621094, 0.004557132720947266, 0.004481077194213867, 0.004392862319946289, 0.0052032470703125, 0.004664182662963867, 0.004359006881713867</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.004750932965959821</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.004557132720947266</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.0004348349176706605</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>0.008944988250732422, 0.00803995132446289, 0.00825190544128418, 0.0077953338623046875, 0.008072853088378906, 0.008026838302612305, 0.008244037628173828</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.008196558271135603</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.008072853088378906</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0003370204815505173</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7735849056603774, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887, 0.8679245283018868, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>0.8804511278195488, 0.7746031746031746, 0.8823529411764706, 0.8707430340557275, 0.8769349845201238, 0.8854489164086687, 0.8591331269349844</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.8613810436455285</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.03634708619100768</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.8546970150743737</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.03902030003424604</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>0.9315068493150684, 0.8181818181818182, 0.8666666666666666, 0.8709677419354839, 0.9117647058823528, 0.888888888888889, 0.8749999999999999</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>0.8571428571428572, 0.7000000000000001, 0.8260869565217391, 0.8181818181818181, 0.8421052631578947, 0.8372093023255814, 0.8095238095238095</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.8128928581219571</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.0483453672097814</v>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>0.8943248532289628, 0.7590909090909091, 0.8463768115942029, 0.8445747800586509, 0.8769349845201238, 0.8630490956072352, 0.8422619047619047</t>
+        </is>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.8466590484088555</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.8463768115942029</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.03990924102038394</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.8804252386957542</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.8749999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.03347823532434504</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8709677419354839, 1.0, 0.9642857142857143, 0.9117647058823529, 0.9655172413793104, 0.9333333333333333</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>0.9375, 0.6363636363636364, 0.7037037037037037, 0.72, 0.8421052631578947, 0.75, 0.7391304347826086</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.7612575768582632</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0.09167272213353993</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.9343722255602084</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0.04187584541475881</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7714285714285715, 0.7647058823529411, 0.7941176470588235, 0.9117647058823529, 0.8235294117647058, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.7777777777777778, 1.0, 0.9473684210526315, 0.8421052631578947, 0.9473684210526315, 0.8947368421052632</t>
+        </is>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.885547201336675</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.07888435511520718</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.8372148859543816</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.07110187882793212</v>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>0.9293233082706767, 0.8690476190476191, 0.9465944272445821, 0.9326625386996904, 0.8707430340557275, 0.9357585139318886, 0.9195046439628483</t>
+        </is>
+      </c>
+      <c r="BR20" t="n">
+        <v>0.9148048693161475</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.9293233082706767</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.02936609269655663</v>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>0.8867924528301887, 0.9059561128526645, 0.9028213166144201, 0.890282131661442, 0.9090909090909091, 0.8840125391849529, 0.8934169278996865</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>0.890351823872221, 0.9054129225502782, 0.9087765271930579, 0.8970701950339376, 0.9176260847151818, 0.8922158261018988, 0.9054901623850846</t>
+        </is>
+      </c>
+      <c r="BW20" t="n">
+        <v>0.9024205059788085</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0.9054129225502782</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0.009011107305991964</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0.8960531985906091</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0.8934169278996865</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>0.009140577155694217</v>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.9253731343283582, 0.9219143576826196, 0.9113924050632911, 0.9265822784810128, 0.905852417302799, 0.9128205128205128</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>0.85, 0.8728813559322034, 0.8713692946058091, 0.8559670781893004, 0.8806584362139918, 0.8489795918367348, 0.8629032258064516</t>
+        </is>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.863251283226356</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0.8629032258064516</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0.01130175620655546</v>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>0.8795454545454545, 0.8991272451302808, 0.8966418261442144, 0.8836797416262958, 0.9036203573475023, 0.8774160045697669, 0.8878618693134822</t>
+        </is>
+      </c>
+      <c r="CI20" t="n">
+        <v>0.8896989283824281</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.8878618693134822</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0.009445118270694173</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>0.9161465735385005</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0.9128205128205128</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0.007715638542056944</v>
+      </c>
+      <c r="CO20" t="inlineStr">
+        <is>
+          <t>0.9424083769633508, 0.9441624365482234, 0.9581151832460733, 0.9523809523809523, 0.9682539682539683, 0.9518716577540107, 0.967391304347826</t>
+        </is>
+      </c>
+      <c r="CP20" t="inlineStr">
+        <is>
+          <t>0.8031496062992126, 0.8442622950819673, 0.8203125, 0.8, 0.823076923076923, 0.7878787878787878, 0.7925925925925926</t>
+        </is>
+      </c>
+      <c r="CQ20" t="n">
+        <v>0.8101818149899263</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>0.8031496062992126</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>0.01847902592158603</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>0.9549405542134864</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>0.009498416528715021</v>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>0.8780487804878049, 0.9073170731707317, 0.8883495145631068, 0.8737864077669902, 0.8883495145631068, 0.8640776699029126, 0.8640776699029126</t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr">
+        <is>
+          <t>0.9026548672566371, 0.9035087719298246, 0.9292035398230089, 0.9203539823008849, 0.9469026548672567, 0.9203539823008849, 0.9469026548672567</t>
+        </is>
+      </c>
+      <c r="CY20" t="n">
+        <v>0.9242686361922505</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0.9203539823008849</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0.01680870046213622</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>0.8805723757653665</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>0.01430691717237729</v>
+      </c>
+      <c r="DE20" t="inlineStr">
+        <is>
+          <t>0.9737103388733002, 0.9790115532734275, 0.9773176389724203, 0.9748689749978521, 0.9757281553398058, 0.9760933069851362, 0.9771458029040296</t>
+        </is>
+      </c>
+      <c r="DF20" t="n">
+        <v>0.9762679673351389</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0.9760933069851362</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>0.001613346821701527</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 8, 'sampling_strategy': 0.84}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9436363636363636</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8522727272727273</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.8952380952380952</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9057239057239057</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.8426966292134831</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9785739170828011</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.8876944684528953</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9196376727441644</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9797979797979798</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.8899082568807339</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9326923076923077</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0.005615711212158203, 0.004361867904663086, 0.003875255584716797, 0.003652811050415039, 0.00399327278137207, 0.003907203674316406, 0.003451824188232422</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.004122563770839146</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.003907203674316406</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.0006634942594281701</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>0.01852107048034668, 0.007456064224243164, 0.0073359012603759766, 0.006966114044189453, 0.0069026947021484375, 0.006920814514160156, 0.006860017776489258</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.008708953857421875</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.006966114044189453</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.004011567349231656</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7547169811320755, 0.9056603773584906, 0.8490566037735849, 0.9056603773584906, 0.8867924528301887, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.8487179487179488, 0.7646520146520146, 0.9130036630036631, 0.8974358974358974, 0.9130036630036631, 0.8772893772893773, 0.8974358974358974</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.8730769230769232</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.8974358974358974</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.04890526345505794</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.8601876809423979</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.04828324697071211</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>0.7741935483870969, 0.6285714285714286, 0.8387096774193549, 0.7777777777777778, 0.8387096774193549, 0.7999999999999999, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.8169014084507042, 0.9333333333333333, 0.8857142857142858, 0.9333333333333333, 0.9210526315789475, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.8978771696022571</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.03785324003346915</v>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>0.841642228739003, 0.7227364185110664, 0.886021505376344, 0.8317460317460318, 0.886021505376344, 0.8605263157894737, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.837205719612042</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.841642228739003</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.05139807108194299</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.7765342696218273</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.06566557818047326</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>0.75, 0.5238095238095238, 0.7647058823529411, 0.6363636363636364, 0.7647058823529411, 0.75, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.90625, 0.9722222222222222, 1.0, 0.9722222222222222, 0.9459459459459459, 1.0</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.9596704317099053</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.03401991342806949</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.6894212230346685</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0.08596725807082888</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>0.8, 0.7857142857142857, 0.9285714285714286, 1.0, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.7435897435897436, 0.8974358974358975, 0.7948717948717948, 0.8974358974358975, 0.8974358974358975, 0.7948717948717948</t>
+        </is>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.06129377483766123</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0.0815305483895436</v>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>0.9512820512820513, 0.8269230769230769, 0.9304029304029304, 0.9642857142857142, 0.9551282051282051, 0.8864468864468864, 0.9514652014652014</t>
+        </is>
+      </c>
+      <c r="BR21" t="n">
+        <v>0.9237048665620096</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0.9512820512820513</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0.04623712896862915</v>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>0.889937106918239, 0.9122257053291536, 0.890282131661442, 0.8934169278996865, 0.8840125391849529, 0.9028213166144201, 0.9028213166144201</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>0.9023199023199023, 0.9251885369532429, 0.9064856711915535, 0.9011312217194569, 0.9059577677224735, 0.9150326797385621, 0.9075414781297134</t>
+        </is>
+      </c>
+      <c r="BW21" t="n">
+        <v>0.9090938939678436</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0.9064856711915535</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0.007770327537237783</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0.8965024348889022</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0.8934169278996865</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>0.009058471311740701</v>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>0.8167539267015707, 0.8526315789473684, 0.8205128205128205, 0.8210526315789475, 0.814070351758794, 0.837696335078534, 0.8342245989304812</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>0.9213483146067417, 0.9375, 0.9209932279909707, 0.9241071428571428, 0.9157175398633256, 0.9306487695749441, 0.9312638580931265</t>
+        </is>
+      </c>
+      <c r="CE21" t="n">
+        <v>0.925939836140893</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0.9241071428571428</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0.006944286040949849</v>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>0.8690511206541562, 0.8950657894736842, 0.8707530242518956, 0.8725798872180451, 0.8648939458110598, 0.8841725523267391, 0.8827442285118039</t>
+        </is>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.8770372211781978</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.8725798872180451</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.009849641424606771</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0.8281346062155023</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0.8210526315789475</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0.0128962089934362</v>
+      </c>
+      <c r="CO21" t="inlineStr">
+        <is>
+          <t>0.7289719626168224, 0.7714285714285715, 0.7272727272727273, 0.7428571428571429, 0.7105263157894737, 0.7547169811320755, 0.7647058823529411</t>
+        </is>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>0.9715639810426541, 0.9813084112149533, 0.9760765550239234, 0.9672897196261683, 0.9804878048780488, 0.9765258215962441, 0.967741935483871</t>
+        </is>
+      </c>
+      <c r="CQ21" t="n">
+        <v>0.9744277469808376</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>0.9760765550239234</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>0.005278541361190964</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>0.7429256547785362</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>0.02040753177903036</v>
+      </c>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>0.9285714285714286, 0.9529411764705882, 0.9411764705882353, 0.9176470588235294, 0.9529411764705882, 0.9411764705882353, 0.9176470588235294</t>
+        </is>
+      </c>
+      <c r="CX21" t="inlineStr">
+        <is>
+          <t>0.8760683760683761, 0.8974358974358975, 0.8717948717948718, 0.8846153846153846, 0.8589743589743589, 0.8888888888888888, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="CY21" t="n">
+        <v>0.882173382173382</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>0.01309377935868574</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>0.9360144057623049</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>0.01392039478277624</v>
+      </c>
+      <c r="DE21" t="inlineStr">
+        <is>
+          <t>0.9793701668701669, 0.9841628959276019, 0.981045751633987, 0.9745852187028657, 0.9773755656108597, 0.9800150829562594, 0.9843891402714932</t>
+        </is>
+      </c>
+      <c r="DF21" t="n">
+        <v>0.980134831710462</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>0.9800150829562594</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>0.003254996682060041</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SVC_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.86}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8659793814432989</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8819444444444444</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8103481812876872</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8078703703703703</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.7547169811320754</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9491525423728814</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.9105691056910569</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.9468005952380952</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.881951219512195</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8946428571428571</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.8533333333333333</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>0.023524761199951172, 0.011916160583496094, 0.011980772018432617, 0.011868000030517578, 0.011543750762939453, 0.011206865310668945, 0.011300325393676758</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.01333437647138323</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.01186800003051758</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.00416975144952451</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>0.009768247604370117, 0.007590055465698242, 0.007718086242675781, 0.007145881652832031, 0.008080244064331055, 0.007833242416381836, 0.007395029067993164</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.007932969502040319</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.007718086242675781</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.0007993330296148551</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.9056603773584906, 0.8301886792452831, 0.8867924528301887, 0.8490566037735849, 0.7924528301886793</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.788888888888889, 0.914860681114551, 0.8560371517027863, 0.8885448916408669, 0.8707430340557275, 0.7801857585139318</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.8580039033157122</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.8707430340557275</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.0500599342577684</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.8546470999301187</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.04939935162878313</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8358208955223881, 0.923076923076923, 0.8524590163934426, 0.9090909090909091, 0.8709677419354839, 0.8358208955223881</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.717948717948718, 0.8780487804878049, 0.7999999999999999, 0.8500000000000001, 0.8181818181818181, 0.717948717948718</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.8101452747794211</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.06499204872905591</v>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.776884806735553, 0.900562851782364, 0.8262295081967213, 0.8795454545454546, 0.8445747800586509, 0.776884806735553</t>
+        </is>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.8459069821029949</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.8445747800586509</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.05215751281968257</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.8816686894265685</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.04067145550645625</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.875, 0.967741935483871, 0.9629629629629629, 0.9375, 0.9642857142857143, 0.8484848484848485</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.6666666666666666, 0.8181818181818182, 0.6923076923076923, 0.8095238095238095, 0.72, 0.7</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.7639794938954603</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.09027351312355102</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0.9249849114480452</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0.04368592993111484</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8, 0.8823529411764706, 0.7647058823529411, 0.8823529411764706, 0.7941176470588235, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7777777777777778, 0.9473684210526315, 0.9473684210526315, 0.8947368421052632, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK22" t="n">
+        <v>0.8705096073517125</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0.08069500846144192</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0.8454981992797118</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0.06578653359117406</v>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>0.9804511278195489, 0.8825396825396825, 0.9473684210526316, 0.9148606811145511, 0.9535603715170279, 0.9256965944272446, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BR22" t="n">
+        <v>0.9224882935630392</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0.9256965944272446</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0.04043575435532779</v>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>0.8584905660377359, 0.8840125391849529, 0.8652037617554859, 0.8808777429467085, 0.8714733542319749, 0.8714733542319749, 0.877742946708464</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>0.872372113101662, 0.8902866923406076, 0.8736575307156972, 0.8857934530457943, 0.8765143053526935, 0.8765143053526935, 0.8793710799896899</t>
+        </is>
+      </c>
+      <c r="BW22" t="n">
+        <v>0.8792156399855483</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0.8765143053526935</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0.006073135727615709</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0.8727534664424711</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0.8714733542319749</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>0.008292606383499008</v>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>0.8825065274151435, 0.9058524173027989, 0.8900255754475703, 0.9040404040404041, 0.8962025316455696, 0.8962025316455696, 0.9022556390977443</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>0.8221343873517787, 0.8489795918367347, 0.8259109311740891, 0.8429752066115702, 0.831275720164609, 0.831275720164609, 0.8368200836820084</t>
+        </is>
+      </c>
+      <c r="CE22" t="n">
+        <v>0.8341959487121999</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>0.831275720164609</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0.008731681275147833</v>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>0.8523204573834611, 0.8774160045697668, 0.8579682533108297, 0.8735078053259872, 0.8637391259050893, 0.8637391259050893, 0.8695378613898763</t>
+        </is>
+      </c>
+      <c r="CI22" t="n">
+        <v>0.8654612333985856</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>0.8637391259050893</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>0.008097961142261292</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>0.8967265180849715</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>0.8962025316455696</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>0.007699777677068657</v>
+      </c>
+      <c r="CO22" t="inlineStr">
+        <is>
+          <t>0.949438202247191, 0.9468085106382979, 0.9405405405405406, 0.9421052631578948, 0.9365079365079365, 0.9365079365079365, 0.9326424870466321</t>
+        </is>
+      </c>
+      <c r="CP22" t="inlineStr">
+        <is>
+          <t>0.7428571428571429, 0.7938931297709924, 0.7611940298507462, 0.7906976744186046, 0.7769230769230769, 0.7769230769230769, 0.7936507936507936</t>
+        </is>
+      </c>
+      <c r="CQ22" t="n">
+        <v>0.7765912749134906</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>0.7769230769230769</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>0.01758513525810435</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>0.9406501252352042</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>0.9405405405405406</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>0.00555135977917238</v>
+      </c>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>0.824390243902439, 0.8682926829268293, 0.8446601941747572, 0.8689320388349514, 0.8592233009708737, 0.8592233009708737, 0.8737864077669902</t>
+        </is>
+      </c>
+      <c r="CX22" t="inlineStr">
+        <is>
+          <t>0.9203539823008849, 0.9122807017543859, 0.9026548672566371, 0.9026548672566371, 0.8938053097345132, 0.8938053097345132, 0.8849557522123894</t>
+        </is>
+      </c>
+      <c r="CY22" t="n">
+        <v>0.9015015414642801</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>0.9026548672566371</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>0.01112585310031572</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0.8569297385068164</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>0.8592233009708737</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>0.01593379294089711</v>
+      </c>
+      <c r="DE22" t="inlineStr">
+        <is>
+          <t>0.946665227714224, 0.9520325203252034, 0.9454635277944841, 0.9473537245467823, 0.9339075521952059, 0.9461293925594982, 0.9476544376664662</t>
+        </is>
+      </c>
+      <c r="DF22" t="n">
+        <v>0.9456009118288379</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>0.946665227714224</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>0.00516610522985337</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.6699999999999999}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9509090909090909</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9142857142857144</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.898989898989899</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.7578947368421053</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9630124259667866</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.8780788177339901</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.9029439089536639</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.9653465346534653</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.8944954128440367</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.9285714285714285</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>0.013010263442993164, 0.021544933319091797, 0.010522127151489258, 0.011262178421020508, 0.011996746063232422, 0.009715080261230469, 0.010497093200683594</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.0126497745513916</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.01126217842102051</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.003767891073714307</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>0.008083820343017578, 0.008440017700195312, 0.006698131561279297, 0.006662845611572266, 0.0065500736236572266, 0.006618022918701172, 0.006651163101196289</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.007100582122802734</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.006662845611572266</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.0007418437669066044</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7358490566037735, 0.9056603773584906, 0.8301886792452831, 0.9056603773584906, 0.8301886792452831, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>0.9358974358974359, 0.728937728937729, 0.8901098901098901, 0.8159340659340659, 0.8901098901098901, 0.7930402930402931, 0.9358974358974359</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.8557038199895343</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.8901098901098901</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.0725136245079178</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.8600878506538884</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.06058394986762905</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.588235294117647, 0.8275862068965518, 0.7096774193548386, 0.8275862068965518, 0.689655172413793, 0.8484848484848484</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>0.9315068493150686, 0.8055555555555556, 0.935064935064935, 0.8799999999999999, 0.935064935064935, 0.8831168831168831, 0.9315068493150686</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.9002594296332065</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.9315068493150686</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.04479920924957068</v>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>0.8943248532289628, 0.6968954248366013, 0.8813255709807435, 0.7948387096774192, 0.8813255709807435, 0.7863860277653381, 0.8899958488999584</t>
+        </is>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.8321560009099667</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.8813255709807435</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.06951731702281097</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.7640525721867268</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.8275862068965518</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.0950721541920841</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>0.75, 0.5, 0.8, 0.6470588235294118, 0.8, 0.6666666666666666, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>1.0, 0.8787878787878788, 0.9473684210526315, 0.9166666666666666, 0.9473684210526315, 0.8947368421052632, 1.0</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.9407040328092959</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0.04415110306432658</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0.7000810850656052</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0.09839510293702024</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>1.0, 0.7142857142857143, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7142857142857143, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7435897435897436, 0.9230769230769231, 0.8461538461538461, 0.9230769230769231, 0.8717948717948718, 0.8717948717948718</t>
+        </is>
+      </c>
+      <c r="BK23" t="n">
+        <v>0.8644688644688644</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0.05603318146805259</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0.8469387755102041</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0.1108446988897981</v>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>0.9641025641025641, 0.8406593406593407, 0.9523809523809523, 0.9230769230769231, 0.9487179487179488, 0.9194139194139195, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="BR23" t="n">
+        <v>0.9336473050758766</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0.9487179487179488</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0.0436420094693025</v>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>0.8805031446540881, 0.8934169278996865, 0.8808777429467085, 0.8746081504702194, 0.8840125391849529, 0.877742946708464, 0.8808777429467085</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>0.8882783882783882, 0.9048768225238814, 0.9038210155857214, 0.8733283056812469, 0.8722473604826546, 0.8792106586224233, 0.8850930115635998</t>
+        </is>
+      </c>
+      <c r="BW23" t="n">
+        <v>0.8866936518197021</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0.8850930115635998</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0.0123772298036695</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0.8817198849729754</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0.8808777429467085</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>0.005495046412788019</v>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>0.8, 0.8229166666666666, 0.8099999999999999, 0.7872340425531914, 0.7955801104972374, 0.7936507936507936, 0.8</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>0.914798206278027, 0.9237668161434976, 0.91324200913242, 0.9111111111111111, 0.9190371991247266, 0.913140311804009, 0.9151785714285714</t>
+        </is>
+      </c>
+      <c r="CE23" t="n">
+        <v>0.9157534607174803</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>0.914798206278027</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0.003980796008433807</v>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>0.8573991031390136, 0.8733417414050821, 0.86162100456621, 0.8491725768321512, 0.8573086548109821, 0.8533955527274013, 0.8575892857142857</t>
+        </is>
+      </c>
+      <c r="CI23" t="n">
+        <v>0.8585468455993038</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>0.8573991031390136</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0.007035821391233857</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>0.801340230481127</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>0.01092453072498818</v>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>0.7169811320754716, 0.7383177570093458, 0.7043478260869566, 0.7184466019417476, 0.75, 0.7211538461538461, 0.7238095238095238</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>0.9622641509433962, 0.9716981132075472, 0.9803921568627451, 0.9490740740740741, 0.9417040358744395, 0.9534883720930233, 0.9579439252336449</t>
+        </is>
+      </c>
+      <c r="CQ23" t="n">
+        <v>0.9595092611841244</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>0.9579439252336449</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>0.01228746994528747</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>0.7247223838681274</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>0.7211538461538461</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>0.01389653012161746</v>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>0.9047619047619048, 0.9294117647058824, 0.9529411764705882, 0.8705882352941177, 0.8470588235294118, 0.8823529411764706, 0.8941176470588236</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.8803418803418803, 0.8547008547008547, 0.8760683760683761, 0.8974358974358975, 0.8760683760683761, 0.8760683760683761</t>
+        </is>
+      </c>
+      <c r="CY23" t="n">
+        <v>0.8760683760683763</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>0.8760683760683761</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>0.01164760929691022</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0.8973189275710285</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>0.03306707380684142</v>
+      </c>
+      <c r="DE23" t="inlineStr">
+        <is>
+          <t>0.9516687016687017, 0.9665661136249372, 0.9544494720965309, 0.9546003016591251, 0.9520864756158873, 0.9588235294117646, 0.9458521870286576</t>
+        </is>
+      </c>
+      <c r="DF23" t="n">
+        <v>0.9548638258722294</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>0.9544494720965309</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0.005999953006957093</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 4, 'sampling_strategy': 0.69}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.95679012345679</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.863608809860578</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.849537037037037</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.9996775793650794</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>0.7724778652191162, 0.7164161205291748, 0.7344160079956055, 0.7523751258850098, 0.7540872097015381, 0.7311298847198486, 0.7327930927276611</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.7419564723968506</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.7344160079956055</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.017310645991385</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>0.008012056350708008, 0.007558107376098633, 0.007194995880126953, 0.008965015411376953, 0.007731914520263672, 0.007369279861450195, 0.007600307464599609</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.007775953837803432</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.007600307464599609</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.0005415263988771391</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8867924528301887, 0.9245283018867925, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8738095238095238, 0.9179566563467492, 0.8475232198142415, 0.9179566563467492, 0.9001547987616099, 0.8506191950464397</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.8936269244539921</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.9001547987616099</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.03481087483242332</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.9003693720674854</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.03613387597360006</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.9142857142857143, 0.9411764705882353, 0.8787878787878787, 0.9411764705882353, 0.90625, 0.8985507246376812</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8333333333333334, 0.8947368421052632, 0.8, 0.8947368421052632, 0.8571428571428571, 0.8108108108108109</t>
+        </is>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.8621721614202816</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.048181180838995</v>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8738095238095238, 0.9179566563467492, 0.8393939393939394, 0.9179566563467492, 0.8816964285714286, 0.8546807677242461</t>
+        </is>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.8919753293608528</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.8816964285714286</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.03844250360955524</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.9217784973014239</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.02923337341369912</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9142857142857143, 0.9411764705882353, 0.90625, 0.9411764705882353, 0.9666666666666667, 0.8857142857142857</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>1.0, 0.8333333333333334, 0.8947368421052632, 0.7619047619047619, 0.8947368421052632, 0.782608695652174, 0.8333333333333334</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.8572362583477326</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.07463639524989529</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0.9287450791127263</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0.02566194126508238</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>1.0, 0.9142857142857143, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.8529411764705882, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8947368421052632, 0.8421052631578947, 0.8947368421052632, 0.9473684210526315, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.8709273182957393</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0.04843646137866588</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0.9163265306122448</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0.04825034408237876</v>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9365079365079365, 0.9814241486068112, 0.9520123839009289, 0.956656346749226, 0.9427244582043344, 0.9427244582043344</t>
+        </is>
+      </c>
+      <c r="BR24" t="n">
+        <v>0.9586494246821535</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0.9520123839009289</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0.0212197147952479</v>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 0.9956140350877193, 0.995575221238938, 0.9931480367729186, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW24" t="n">
+        <v>0.9958661366880558</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0.001885242517235258</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0.9968637954974975</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>0.001675622622249898</v>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9951456310679612, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 0.9955947136563876, 0.9955555555555555, 0.9911504424778761, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE24" t="n">
+        <v>0.9955667683366408</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0.002365186821933608</v>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 0.9965808118160284, 0.9965671240247511, 0.9931480367729186, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI24" t="n">
+        <v>0.9965702076326874</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>0.001831273974945286</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>0.9975736469287341</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>0.001297393947929273</v>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951456310679612, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9911504424778761, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ24" t="n">
+        <v>0.9987357774968394</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>0.003096700054087461</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>0.9958491627972421</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>0.001694606963530478</v>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9912280701754386, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY24" t="n">
+        <v>0.9924257546521169</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>0.003092288713291248</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>0.9993065187239945</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>0.001698675272387779</v>
+      </c>
+      <c r="DE24" t="inlineStr">
+        <is>
+          <t>0.9993740556874595, 0.9999572100984168, 0.999720766388865, 0.9996778073717674, 0.9994200532691812, 1.0, 0.9995918893375719</t>
+        </is>
+      </c>
+      <c r="DF24" t="n">
+        <v>0.9996773974504659</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>0.9996778073717674</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>0.000223543682521891</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 4, 'sampling_strategy': 0.74}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8837209302325583</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9845454545454545</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9184959791349707</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9386363636363636</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9807692307692307</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9532710280373831</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9932659932659933</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.9998838694692835</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.9914458525345622</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.9908256880733946</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.9953917050691244</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>0.7122321128845215, 0.7728009223937988, 0.813277006149292, 0.7296872138977051, 0.7724158763885498, 0.7290596961975098, 0.7153401374816895</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.7492589950561523</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.7296872138977051</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.03484929684623403</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>0.006712913513183594, 0.006844282150268555, 0.0064830780029296875, 0.007690906524658203, 0.006407022476196289, 0.007657051086425781, 0.006745100021362305</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.006934336253574916</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.006745100021362305</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.0004883437396467401</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8679245283018868, 0.9245283018867925, 0.8867924528301887, 0.9811320754716981, 0.9245283018867925, 0.9622641509433962</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>0.8871794871794871, 0.8873626373626373, 0.88003663003663, 0.8772893772893773, 0.9642857142857143, 0.9029304029304028, 0.9743589743589743</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.9104918890633176</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.8873626373626373</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.03805694275887617</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.9247279624638115</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.03636646272653015</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.7878787878787878, 0.8461538461538461, 0.7999999999999999, 0.962962962962963, 0.8571428571428571, 0.9333333333333333</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>0.9500000000000001, 0.9041095890410958, 0.9500000000000001, 0.9210526315789475, 0.9873417721518987, 0.9487179487179487, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.9478437360023152</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.02637186560028442</v>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>0.9035714285714286, 0.8459941884599418, 0.8980769230769231, 0.8605263157894737, 0.9751523675574308, 0.9029304029304028, 0.9535087719298245</t>
+        </is>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.9056800569022035</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.9029304029304028</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.04273684544732416</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.8635163778020921</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.0596443110384235</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>0.9230769230769231, 0.6842105263157895, 0.9166666666666666, 0.75, 1.0, 0.8571428571428571, 0.875</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>0.926829268292683, 0.9705882352941176, 0.926829268292683, 0.9459459459459459, 0.975, 0.9487179487179487, 1.0</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.9562729523633398</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0.02497218606634411</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0.8580138533146051</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0.09999807013055639</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>0.8, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.8461538461538461, 0.9743589743589743, 0.8974358974358975, 1.0, 0.9487179487179487, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0.04887056433745909</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0.8795918367346938</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0.07116569703739875</v>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>0.9726495726495726, 0.9212454212454212, 0.989010989010989, 0.9340659340659341, 0.9963369963369964, 0.9175824175824175, 0.9890109890109889</t>
+        </is>
+      </c>
+      <c r="BR25" t="n">
+        <v>0.9599860457003314</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0.9726495726495726</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0.03193163913115357</v>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>0.9905660377358491, 1.0, 0.9937304075235109, 1.0, 0.9937304075235109, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>0.9897741147741148, 1.0, 0.9957264957264957, 1.0, 0.9957264957264957, 0.9978632478632479, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="BW25" t="n">
+        <v>0.9964024071166928</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0.003236493534581461</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0.9955174948668768</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.9937304075235109</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>0.003297184839074249</v>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>0.9822485207100591, 1.0, 0.9883720930232558, 1.0, 0.9883720930232558, 0.9941520467836257, 0.9883720930232558</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>0.9935760171306209, 1.0, 0.9957081545064378, 1.0, 0.9957081545064378, 0.9978586723768736, 0.9957081545064378</t>
+        </is>
+      </c>
+      <c r="CE25" t="n">
+        <v>0.9969370218609724</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0.9957081545064378</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0.002250073254564664</v>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>0.98791226892034, 1.0, 0.9920401237648468, 1.0, 0.9920401237648468, 0.9960053595802496, 0.9920401237648468</t>
+        </is>
+      </c>
+      <c r="CI25" t="n">
+        <v>0.9942911428278756</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>0.9920401237648468</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>0.004209036745794644</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0.9916452637947789</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>0.9883720930232558</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>0.006168200899657224</v>
+      </c>
+      <c r="CO25" t="inlineStr">
+        <is>
+          <t>0.9764705882352941, 1.0, 0.9770114942528736, 1.0, 0.9770114942528736, 0.9883720930232558, 0.9770114942528736</t>
+        </is>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>0.9957081545064378, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ25" t="n">
+        <v>0.9993868792152055</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>0.001501833073441548</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>0.98512530914531</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>0.9770114942528736</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>0.01018023738112035</v>
+      </c>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>0.9914529914529915, 1.0, 0.9914529914529915, 1.0, 0.9914529914529915, 0.9957264957264957, 0.9914529914529915</t>
+        </is>
+      </c>
+      <c r="CY25" t="n">
+        <v>0.9945054945054945</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>0.9914529914529915</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>0.003763378512191059</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>0.9982993197278912</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>0.004165798882284302</v>
+      </c>
+      <c r="DE25" t="inlineStr">
+        <is>
+          <t>0.9998982498982499, 1.0, 0.9999497234791352, 1.0, 0.9998994469582705, 1.0, 0.9998994469582705</t>
+        </is>
+      </c>
+      <c r="DF25" t="n">
+        <v>0.9999495524705608</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>0.9999497234791352</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>4.673323621967875e-05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 0.94}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9448302469135803</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8366013071895425</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8287037037037037</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>0.24402308464050293, 0.23041105270385742, 0.2530517578125, 0.23421120643615723, 0.26566410064697266, 0.24448013305664062, 0.23070001602172852</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.2432201930454799</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.2440230846405029</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.01197981329846138</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>0.007908821105957031, 0.0075871944427490234, 0.007344961166381836, 0.0076138973236083984, 0.00824594497680664, 0.007623910903930664, 0.007910966873168945</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.007747956684657505</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.007623910903930664</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.0002730910828933197</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8113207547169812, 0.9056603773584906, 0.8679245283018868, 0.9056603773584906, 0.8113207547169812, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8166666666666667, 0.903250773993808, 0.8738390092879257, 0.903250773993808, 0.8413312693498451, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.8803774141235442</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.03995075185320381</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.8788060297494261</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.05044858216712458</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8484848484848486, 0.9253731343283583, 0.8923076923076922, 0.9253731343283583, 0.8333333333333333, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7499999999999999, 0.8717948717948718, 0.8292682926829269, 0.8717948717948718, 0.782608695652174, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.8417166342181691</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.0590680060591041</v>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.7992424242424243, 0.898584003061615, 0.8607879924953096, 0.898584003061615, 0.8079710144927537, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.8714911078867392</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.05128142114621656</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.9012655815553094</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.9117647058823528</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.04438188913042727</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9032258064516129, 0.9393939393939394, 0.9354838709677419, 0.9393939393939394, 0.9615384615384616, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>1.0, 0.6818181818181818, 0.85, 0.7727272727272727, 0.85, 0.6666666666666666, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.809045340624288</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0.1060246921752263</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0.933820952796285</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0.0185268084276829</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.9117647058823529, 0.8529411764705882, 0.9117647058823529, 0.7352941176470589, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK26" t="n">
+        <v>0.8859649122807018</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0.03539961627023942</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0.8747899159663867</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0.08045313374723648</v>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>0.9969924812030075, 0.946031746031746, 0.9736842105263157, 0.953560371517028, 0.9427244582043344, 0.9643962848297214, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BR26" t="n">
+        <v>0.9597951461286269</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.953560371517028</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0.01876198811273485</v>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW26" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE26" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI26" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO26" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP26" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX26" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY26" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE26" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914511, 0.9999785204914511, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF26" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>0.9999785204914511</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>9.712984233473657e-06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 4, 'sampling_strategy': 0.95}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8837209302325583</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9909090909090909</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9184959791349707</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.9386363636363636</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9807692307692307</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.9532710280373831</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>0.16175580024719238, 0.13829398155212402, 0.13585281372070312, 0.12361907958984375, 0.13568997383117676, 0.13245916366577148, 0.13080596923828125</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.136925254549299</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.1356899738311768</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.01105538894835609</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>0.0070972442626953125, 0.0069010257720947266, 0.006963253021240234, 0.00666499137878418, 0.006618976593017578, 0.006672859191894531, 0.006839752197265625</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.006822586059570312</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.006839752197265625</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.0001649167844787015</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8301886792452831, 0.9245283018867925, 0.8679245283018868, 0.9245283018867925, 0.9056603773584906, 0.9622641509433962</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>0.8205128205128205, 0.7930402930402931, 0.88003663003663, 0.8644688644688645, 0.88003663003663, 0.8672161172161172, 0.9514652014652014</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.8652537938252225</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.04643041262533829</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.9005690326445043</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.03988516757013834</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>0.7692307692307692, 0.689655172413793, 0.8461538461538461, 0.7741935483870968, 0.8461538461538461, 0.8148148148148148, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>0.9268292682926831, 0.8831168831168831, 0.9500000000000001, 0.9066666666666667, 0.9500000000000001, 0.9367088607594937, 0.9743589743589743</t>
+        </is>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.932525807599243</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.9367088607594937</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.02808302518134371</v>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>0.8480300187617261, 0.7863860277653381, 0.8980769230769231, 0.8404301075268817, 0.8980769230769231, 0.8757618377871542, 0.9514652014652014</t>
+        </is>
+      </c>
+      <c r="AU27" t="n">
+        <v>0.8711752913514497</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.04867544239200444</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.8098247751036565</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.0698196268492996</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.6666666666666666, 0.9166666666666666, 0.7058823529411765, 0.9166666666666666, 0.8461538461538461, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>0.8837209302325582, 0.8947368421052632, 0.926829268292683, 0.9444444444444444, 0.926829268292683, 0.925, 0.9743589743589743</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.9251313896752293</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0.02787929774273378</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0.8413855052510515</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0.1017212067927876</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.8717948717948718, 0.9743589743589743, 0.8717948717948718, 0.9743589743589743, 0.9487179487179487, 0.9743589743589743</t>
+        </is>
+      </c>
+      <c r="BK27" t="n">
+        <v>0.9413919413919415</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.9743589743589743</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0.04486244950152339</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0.7891156462585034</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0.07991387839776008</v>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>0.9623931623931624, 0.9120879120879121, 0.9761904761904762, 0.9285714285714285, 0.9908424908424909, 0.9285714285714285, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="BR27" t="n">
+        <v>0.9551194836909123</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0.9623931623931624</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0.02942832650525159</v>
+      </c>
+      <c r="BU27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE27" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 8, 'sampling_strategy': 0.9099999999999999}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8210526315789474</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8460648148148149</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7559808612440191</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.7581018518518519</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6909090909090909</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.9494949494949495</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9633507853403142</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9608355091383812</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.9922371031746032</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9448727308725082</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.9458333333333333</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.9289099526066351</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>0.032070159912109375, 0.03020620346069336, 0.03063821792602539, 0.031116008758544922, 0.030673980712890625, 0.03023505210876465, 0.030229806900024414</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.03073848996843611</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.03063821792602539</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.0006239984284861761</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>0.009537935256958008, 0.009442806243896484, 0.009402990341186523, 0.00956583023071289, 0.009371042251586914, 0.009244918823242188, 0.00923919677734375</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.009400674274989538</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.009402990341186523</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.0001189899957705615</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774, 0.9056603773584906, 0.8113207547169812, 0.8113207547169812</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.788888888888889, 0.8359133126934984, 0.7654798761609907, 0.903250773993808, 0.8297213622291022, 0.8065015479876161</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.8283109735122119</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.8297213622291022</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.0435267987938192</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.8358290905460716</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.04947147335826674</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8358208955223881, 0.8823529411764706, 0.8181818181818182, 0.9253731343283583, 0.8387096774193549, 0.8484848484848485</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>0.8484848484848484, 0.717948717948718, 0.7894736842105263, 0.7, 0.8717948717948718, 0.7727272727272727, 0.7500000000000001</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.7786327707380339</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.05903557354626853</v>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>0.8909090909090909, 0.776884806735553, 0.8359133126934984, 0.759090909090909, 0.898584003061615, 0.8057184750733137, 0.7992424242424243</t>
+        </is>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.8237632888294864</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.8057184750733137</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.05008752052028431</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.8688938069209389</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.04228583993325178</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>0.875, 0.875, 0.8823529411764706, 0.84375, 0.9393939393939394, 0.9285714285714286, 0.875</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>1.0, 0.6666666666666666, 0.7894736842105263, 0.6666666666666666, 0.85, 0.68, 0.7142857142857143</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>0.7667275331185105</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0.1147443732131228</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0.8884383298774056</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0.03112872964353227</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.8823529411764706, 0.7941176470588235, 0.9117647058823529, 0.7647058823529411, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.7777777777777778, 0.7894736842105263, 0.7368421052631579, 0.8947368421052632, 0.8947368421052632, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK28" t="n">
+        <v>0.8028404344193818</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0.06162899963745361</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0.853781512605042</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0.07640129837096274</v>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>0.9293233082706768, 0.8841269841269841, 0.9318885448916409, 0.8839009287925697, 0.943498452012384, 0.8351393188854489, 0.8854489164086689</t>
+        </is>
+      </c>
+      <c r="BR28" t="n">
+        <v>0.899046636198339</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0.8854489164086689</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0.03523850051115178</v>
+      </c>
+      <c r="BU28" t="inlineStr">
+        <is>
+          <t>0.9150943396226415, 0.9122257053291536, 0.896551724137931, 0.9122257053291536, 0.890282131661442, 0.9435736677115988, 0.9216300940438872</t>
+        </is>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>0.9162745521260522, 0.910290971330766, 0.8979293753758915, 0.9080677034109459, 0.8830870349686399, 0.9483203024314804, 0.9153492568090043</t>
+        </is>
+      </c>
+      <c r="BW28" t="n">
+        <v>0.9113313137789686</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0.910290971330766</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0.0185081042349545</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0.9130833382622582</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0.9122257053291536</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>0.01604196152637668</v>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>0.9326683291770573, 0.9306930693069306, 0.9177057356608479, 0.9313725490196079, 0.9144254278728607, 0.9552238805970149, 0.9391727493917275</t>
+        </is>
+      </c>
+      <c r="CD28" t="inlineStr">
+        <is>
+          <t>0.8851063829787233, 0.8803418803418803, 0.8607594936708861, 0.8782608695652174, 0.8471615720524018, 0.9237288135593221, 0.8898678414096916</t>
+        </is>
+      </c>
+      <c r="CE28" t="n">
+        <v>0.8807466933683032</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0.8803418803418803</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0.02230777126064853</v>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>0.9088873560778903, 0.9055174748244055, 0.889232614665867, 0.9048167092924126, 0.8807934999626312, 0.9394763470781685, 0.9145202954007094</t>
+        </is>
+      </c>
+      <c r="CI28" t="n">
+        <v>0.9061777567574408</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>0.9055174748244055</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>0.01740083229865369</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>0.9316088201465781</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>0.9313725490196079</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>0.01256676920058063</v>
+      </c>
+      <c r="CO28" t="inlineStr">
+        <is>
+          <t>0.9540816326530612, 0.9447236180904522, 0.9435897435897436, 0.9405940594059405, 0.9211822660098522, 0.9795918367346939, 0.9414634146341463</t>
+        </is>
+      </c>
+      <c r="CP28" t="inlineStr">
+        <is>
+          <t>0.8524590163934426, 0.8583333333333333, 0.8225806451612904, 0.8632478632478633, 0.8362068965517241, 0.8861788617886179, 0.8859649122807017</t>
+        </is>
+      </c>
+      <c r="CQ28" t="n">
+        <v>0.8578530755367105</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>0.8583333333333333</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>0.02192114829235909</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>0.9464609387311272</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>0.9435897435897436</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>0.01632439120539962</v>
+      </c>
+      <c r="CW28" t="inlineStr">
+        <is>
+          <t>0.9121951219512195, 0.9170731707317074, 0.8932038834951457, 0.9223300970873787, 0.9077669902912622, 0.9320388349514563, 0.9368932038834952</t>
+        </is>
+      </c>
+      <c r="CX28" t="inlineStr">
+        <is>
+          <t>0.9203539823008849, 0.9035087719298246, 0.9026548672566371, 0.8938053097345132, 0.8584070796460177, 0.9646017699115044, 0.8938053097345132</t>
+        </is>
+      </c>
+      <c r="CY28" t="n">
+        <v>0.9053052986448422</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>0.9026548672566371</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>0.02980107647714419</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>0.9173573289130951</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>0.9170731707317074</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>0.01375301577710595</v>
+      </c>
+      <c r="DE28" t="inlineStr">
+        <is>
+          <t>0.979451759119361, 0.9842747111681643, 0.9808402783744308, 0.9844917948277343, 0.9786064094853509, 0.9932554343156629, 0.9836111349772317</t>
+        </is>
+      </c>
+      <c r="DF28" t="n">
+        <v>0.9835045031811337</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>0.9836111349772317</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>0.004538315350948044</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 4, 'sampling_strategy': 0.84}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9304545454545455</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7805183946488294</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8090909090909091</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9461279461279462</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.9036144578313253</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.9933805597491581</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.9331156401306159</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.947160608523981</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9809523809523809</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.944954128440367</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.9626168224299064</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>0.03228020668029785, 0.03156614303588867, 0.031677961349487305, 0.03077411651611328, 0.03044414520263672, 0.031076908111572266, 0.03061199188232422</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.03120449611118862</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.03107690811157227</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.0006144464544120479</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>0.009086847305297852, 0.008793830871582031, 0.008942842483520508, 0.008946895599365234, 0.008803844451904297, 0.008793115615844727, 0.008880853652954102</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.008892604282924108</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.008880853652954102</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.000100621172263454</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.8113207547169812, 0.9245283018867925, 0.7924528301886793, 0.8490566037735849, 0.8867924528301887, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>0.8153846153846154, 0.8031135531135531, 0.9029304029304028, 0.7902930402930403, 0.8287545787545787, 0.8543956043956045, 0.8516483516483516</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.8352171637885923</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.8287545787545787</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.03526793960001361</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.8521513427173806</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.04086340408884092</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.6875000000000001, 0.8571428571428571, 0.6666666666666667, 0.7333333333333334, 0.7857142857142857, 0.75</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.8648648648648648, 0.9487179487179487, 0.8493150684931507, 0.8947368421052632, 0.9230769230769231, 0.8918918918918919</t>
+        </is>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.895719919512277</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.03089430404276664</v>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>0.8153846153846154, 0.7761824324324325, 0.9029304029304028, 0.7579908675799087, 0.8140350877192983, 0.8543956043956045, 0.8209459459459459</t>
+        </is>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.8202664223411725</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.8153846153846154</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.04453393724263804</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.744812925170068</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.05852107291245863</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.6111111111111112, 0.8571428571428571, 0.5789473684210527, 0.6875, 0.7857142857142857, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.9142857142857143, 0.9487179487179487, 0.9117647058823529, 0.918918918918919, 0.9230769230769231, 0.9428571428571428</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.9224367501678427</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0.01658679916324319</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0.7029165174841868</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0.09017025183284708</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.8205128205128205, 0.9487179487179487, 0.7948717948717948, 0.8717948717948718, 0.9230769230769231, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK29" t="n">
+        <v>0.8717948717948719</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0.05128205128205129</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0.7986394557823129</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0.04101990049437097</v>
+      </c>
+      <c r="BQ29" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.8882783882783882, 0.9688644688644689, 0.9120879120879122, 0.9395604395604396, 0.9285714285714286, 0.8553113553113553</t>
+        </is>
+      </c>
+      <c r="BR29" t="n">
+        <v>0.9084772370486657</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0.9120879120879122</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0.03781973222722747</v>
+      </c>
+      <c r="BU29" t="inlineStr">
+        <is>
+          <t>0.9622641509433962, 0.9717868338557993, 0.9529780564263323, 0.9592476489028213, 0.9529780564263323, 0.9529780564263323, 0.9529780564263323</t>
+        </is>
+      </c>
+      <c r="BV29" t="inlineStr">
+        <is>
+          <t>0.9667277167277167, 0.9770236299648065, 0.9529663147310206, 0.9647310206133735, 0.9567119155354449, 0.9492207139265962, 0.9567119155354449</t>
+        </is>
+      </c>
+      <c r="BW29" t="n">
+        <v>0.9605847467192007</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0.9567119155354449</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0.008802142110380573</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0.9578872656296208</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0.9529780564263323</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>0.006661264407868506</v>
+      </c>
+      <c r="CC29" t="inlineStr">
+        <is>
+          <t>0.9318181818181818, 0.9491525423728814, 0.9152542372881357, 0.9273743016759776, 0.9162011173184357, 0.9142857142857143, 0.9162011173184357</t>
+        </is>
+      </c>
+      <c r="CD29" t="inlineStr">
+        <is>
+          <t>0.9739130434782609, 0.9804772234273319, 0.9674620390455531, 0.971677559912854, 0.9673202614379085, 0.9676025917926566, 0.9673202614379085</t>
+        </is>
+      </c>
+      <c r="CE29" t="n">
+        <v>0.970824711504639</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0.9676025917926566</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0.004624285168700967</v>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>0.9528656126482213, 0.9648148829001066, 0.9413581381668443, 0.9495259307944157, 0.941760689378172, 0.9409441530391854, 0.941760689378172</t>
+        </is>
+      </c>
+      <c r="CI29" t="n">
+        <v>0.9475757280435883</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>0.941760689378172</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0.008274230135458185</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0.9243267445825375</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>0.9162011173184357</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>0.01193382819024105</v>
+      </c>
+      <c r="CO29" t="inlineStr">
+        <is>
+          <t>0.8913043478260869, 0.9130434782608695, 0.8804347826086957, 0.8829787234042553, 0.8723404255319149, 0.8888888888888888, 0.8723404255319149</t>
+        </is>
+      </c>
+      <c r="CP29" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9955947136563876, 0.9823788546255506, 0.9911111111111112, 0.9866666666666667, 0.9781659388646288, 0.9866666666666667</t>
+        </is>
+      </c>
+      <c r="CQ29" t="n">
+        <v>0.9873906277241267</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>0.005431998092925895</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>0.885904438864661</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>0.8829787234042553</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>0.01298920037120543</v>
+      </c>
+      <c r="CW29" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9882352941176471, 0.9529411764705882, 0.9764705882352941, 0.9647058823529412, 0.9411764705882353, 0.9647058823529412</t>
+        </is>
+      </c>
+      <c r="CX29" t="inlineStr">
+        <is>
+          <t>0.9572649572649573, 0.9658119658119658, 0.9529914529914529, 0.9529914529914529, 0.9487179487179487, 0.9572649572649573, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="CY29" t="n">
+        <v>0.9548229548229549</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>0.9529914529914529</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>0.005528318155151073</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>0.9663465386154463</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>0.01462452279951125</v>
+      </c>
+      <c r="DE29" t="inlineStr">
+        <is>
+          <t>0.995395807895808, 0.9970085470085469, 0.9927601809954751, 0.9970839617898442, 0.9959527400703871, 0.9952237305178482, 0.9925339366515837</t>
+        </is>
+      </c>
+      <c r="DF29" t="n">
+        <v>0.995136986418499</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>0.9953958078958079</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>0.001709573520888238</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.8999999999999999}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9533179012345678</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>0.0649411678314209, 0.06500005722045898, 0.0632028579711914, 0.06237912178039551, 0.0677499771118164, 0.062252044677734375, 0.06173086166381836</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.0638937268938337</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.06320285797119141</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.001976150662013262</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>0.010500669479370117, 0.010692834854125977, 0.010670900344848633, 0.010185956954956055, 0.00957489013671875, 0.01076817512512207, 0.010215044021606445</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.01037263870239258</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.01050066947937012</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.0003892144940733219</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8867924528301887, 0.8867924528301887, 0.8490566037735849, 0.9622641509433962, 0.8113207547169812, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.8738095238095238, 0.8769349845201238, 0.8475232198142415, 0.9473684210526316, 0.8297213622291022, 0.8243034055727554</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.8743876497967608</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.8738095238095238</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.04265449734207535</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.8842467804731956</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.05002618177810771</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.9142857142857143, 0.9117647058823528, 0.8787878787878787, 0.9714285714285714, 0.8387096774193549, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>0.9142857142857143, 0.8333333333333334, 0.8421052631578947, 0.8, 0.9444444444444444, 0.7727272727272727, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.8406676865323481</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.06149330978186609</v>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>0.9365949119373776, 0.8738095238095238, 0.8769349845201238, 0.8393939393939394, 0.9579365079365079, 0.8057184750733137, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.8745906249166883</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.8738095238095238</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.05156828043059845</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.9085135633010285</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.9117647058823528</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.04279085169319258</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.9142857142857143, 0.9117647058823529, 0.90625, 0.9444444444444444, 0.9285714285714286, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>1.0, 0.8333333333333334, 0.8421052631578947, 0.7619047619047619, 1.0, 0.68, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.8486961100229565</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.1086867495936684</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.9124971479819999</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.02401040141082343</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>1.0, 0.9142857142857143, 0.9117647058823529, 0.8529411764705882, 1.0, 0.7647058823529411, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8333333333333334, 0.8421052631578947, 0.8421052631578947, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.8408521303258144</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.04882395924505805</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0.907923169267707</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0.0761206684010938</v>
+      </c>
+      <c r="BQ30" t="inlineStr">
+        <is>
+          <t>0.9969924812030075, 0.946031746031746, 0.976780185758514, 0.9342105263157895, 0.9512383900928792, 0.9195046439628484, 0.9411764705882354</t>
+        </is>
+      </c>
+      <c r="BR30" t="n">
+        <v>0.9522763491361458</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0.946031746031746</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0.02438854772535699</v>
+      </c>
+      <c r="BU30" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV30" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW30" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC30" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD30" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE30" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI30" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO30" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP30" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW30" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX30" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY30" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE30" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF30" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>9.712984233453662e-06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.75}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8636363636363635</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9804545454545455</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9035162950257289</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.9295454545454545</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.9433962264150944</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>0.0796051025390625, 0.07997727394104004, 0.0634450912475586, 0.0623631477355957, 0.06535506248474121, 0.06170320510864258, 0.0623321533203125</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.06782586233956474</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.06344509124755859</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.007645842306855208</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>0.015337944030761719, 0.010304927825927734, 0.009552001953125, 0.009431838989257812, 0.010364770889282227, 0.009452104568481445, 0.009713888168334961</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.01059392520359584</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.009713888168334961</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.001969627005740714</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.8113207547169812, 0.9056603773584906, 0.7924528301886793, 0.9811320754716981, 0.9056603773584906, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>0.8076923076923077, 0.7802197802197802, 0.8672161172161172, 0.7673992673992673, 0.9642857142857143, 0.8901098901098901, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.8593668236525379</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.07140652483304702</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.8871418588399721</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.06288392998537401</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.6666666666666666, 0.8148148148148148, 0.6451612903225806, 0.962962962962963, 0.8275862068965518, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>0.9135802469135802, 0.868421052631579, 0.9367088607594937, 0.8533333333333333, 0.9873417721518987, 0.935064935064935, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.9222127374133974</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.935064935064935</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.04446028875597272</v>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>0.8271604938271605, 0.7675438596491229, 0.8757618377871542, 0.749247311827957, 0.9751523675574308, 0.8813255709807435, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.857855254888288</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.07611702634239123</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.7934977723631784</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.1081190819230792</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.625, 0.8461538461538461, 0.5882352941176471, 1.0, 0.8, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.8918918918918919, 0.925, 0.8888888888888888, 0.975, 0.9473684210526315, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.9261122561874442</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.03722938687595029</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.7941984486102134</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0.1325138363331433</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 0.7857142857142857, 0.7142857142857143, 0.9285714285714286, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8461538461538461, 0.9487179487179487, 0.8205128205128205, 1.0, 0.9230769230769231, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.9194139194139195</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0.05883655093116854</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0.7993197278911565</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0.09928244570970358</v>
+      </c>
+      <c r="BQ31" t="inlineStr">
+        <is>
+          <t>0.9547008547008548, 0.8736263736263736, 0.9725274725274725, 0.9075091575091575, 0.9963369963369964, 0.9294871794871795, 0.9816849816849818</t>
+        </is>
+      </c>
+      <c r="BR31" t="n">
+        <v>0.945124716553288</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0.9547008547008548</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0.04066138907917714</v>
+      </c>
+      <c r="BU31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE31" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 0.9999999999999999, 1.0</t>
+        </is>
+      </c>
+      <c r="DF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>4.196248604251576e-17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_splashing_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 0.88}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9498456790123457</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8528257456828885</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9999751984126983</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>0.45603513717651367, 0.4394669532775879, 0.46507883071899414, 0.4680771827697754, 0.42835283279418945, 0.4612758159637451, 0.45145177841186523</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.452819790158953</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.4560351371765137</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.01332943383857067</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>0.009252786636352539, 0.008599042892456055, 0.007678031921386719, 0.008246898651123047, 0.00859212875366211, 0.00799703598022461, 0.007942914962768555</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.008329834256853377</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.008246898651123047</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.0004906698948001291</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8490566037735849, 0.9622641509433962, 0.8679245283018868, 0.8867924528301887, 0.8301886792452831, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8452380952380952, 0.9589783281733746, 0.8622291021671826, 0.8885448916408669, 0.8444272445820433, 0.8243034055727554</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.8815842126324214</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.8622291021671826</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.04887776873117254</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.8868922831186982</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.05057643216738573</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8823529411764706, 0.9705882352941176, 0.8955223880597014, 0.9090909090909091, 0.8571428571428571, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7894736842105262, 0.9473684210526315, 0.8205128205128205, 0.8500000000000001, 0.7906976744186046, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.8457535460595436</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.06712448964047268</v>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8359133126934983, 0.9589783281733746, 0.858017604286261, 0.8795454545454546, 0.8239202657807309, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU32" t="n">
+        <v>0.8780649043655263</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.8580176042862609</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.05378253253251361</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.9103762626715091</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.8955223880597014</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.04123107220097742</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9090909090909091, 0.9705882352941176, 0.9090909090909091, 0.9375, 0.9310344827586207, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>1.0, 0.75, 0.9473684210526315, 0.8, 0.8095238095238095, 0.7083333333333334, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.8341078536677828</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.09645216852661227</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0.9234802276130877</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0.03225236501798741</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9705882352941176, 0.8823529411764706, 0.8823529411764706, 0.7941176470588235, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.8421052631578947, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK32" t="n">
+        <v>0.8634085213032581</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0.06253120275626391</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0.8997599039615846</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0.06413306309336415</v>
+      </c>
+      <c r="BQ32" t="inlineStr">
+        <is>
+          <t>0.9894736842105263, 0.953968253968254, 0.9907120743034056, 0.9504643962848297, 0.958204334365325, 0.9287925696594428, 0.931888544891641</t>
+        </is>
+      </c>
+      <c r="BR32" t="n">
+        <v>0.9576434082404892</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0.953968253968254</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0.02289025565031859</v>
+      </c>
+      <c r="BU32" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV32" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW32" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC32" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE32" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH32" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI32" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO32" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP32" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW32" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX32" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY32" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE32" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF32" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>9.712984233443666e-06</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_no_fragmentation_smote_optuna-opt-mean-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.88}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.989090909090909</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9133749133749134</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.9068181818181817</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9464285714285714</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9549549549549549</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>0.2822110652923584, 0.2980480194091797, 0.2828841209411621, 0.262113094329834, 0.33215999603271484, 0.27501392364501953, 0.18818402290344238</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.2743734632219587</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.2822110652923584</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.04073077766316177</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>0.006906747817993164, 0.006883144378662109, 0.006227970123291016, 0.006373167037963867, 0.0067291259765625, 0.00652003288269043, 0.006187915802001953</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.006546872002737862</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.00652003288269043</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.0002770373724411881</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.8679245283018868, 0.9433962264150944, 0.8867924528301887, 0.9245283018867925, 0.9433962264150944, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>0.8076923076923077, 0.8644688644688645, 0.9157509157509157, 0.8772893772893773, 0.88003663003663, 0.9157509157509157, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.8838304552590267</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.88003663003663</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.03785380087836552</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.9087052011580316</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.03052040668497827</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.7741935483870968, 0.888888888888889, 0.7999999999999999, 0.8461538461538461, 0.888888888888889, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>0.9135802469135802, 0.9066666666666667, 0.9620253164556962, 0.9210526315789475, 0.9500000000000001, 0.9620253164556962, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.937531228446174</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.02154721116260996</v>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>0.8271604938271605, 0.8404301075268817, 0.9254571026722926, 0.8605263157894737, 0.8980769230769231, 0.9254571026722926, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.8834465127749535</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.8980769230769231</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.037499112786372</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.8293617971037326</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.05414256042248849</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.7058823529411765, 0.9230769230769231, 0.75, 0.9166666666666666, 0.9230769230769231, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9444444444444444, 0.95, 0.9459459459459459, 0.926829268292683, 0.95, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.9387350018012039</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.02670262761839431</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.8377908855850034</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0.08153474672553987</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8717948717948718, 0.9743589743589743, 0.8974358974358975, 0.9743589743589743, 0.9743589743589743, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK33" t="n">
+        <v>0.9377289377289377</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0.03841790652637916</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0.8299319727891156</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0.07681353599072255</v>
+      </c>
+      <c r="BQ33" t="inlineStr">
+        <is>
+          <t>0.9709401709401709, 0.9157509157509157, 0.989010989010989, 0.9432234432234432, 0.9908424908424909, 0.9157509157509157, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="BR33" t="n">
+        <v>0.9589569160997733</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0.9709401709401709</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0.03126181648864199</v>
+      </c>
+      <c r="BU33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE33" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 0.9999999999999999, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>4.196248604251576e-17</v>
       </c>
     </row>
   </sheetData>
